--- a/lay0x3/Sinais_Arsenal_Completo_Paper_Trading_01_a_17_Ago.xlsx
+++ b/lay0x3/Sinais_Arsenal_Completo_Paper_Trading_01_a_17_Ago.xlsx
@@ -473,7 +473,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:K1809"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>

--- a/lay0x3/Sinais_Arsenal_Completo_Paper_Trading_01_a_17_Ago.xlsx
+++ b/lay0x3/Sinais_Arsenal_Completo_Paper_Trading_01_a_17_Ago.xlsx
@@ -15484,10 +15484,20 @@
       <c r="G307" s="2" t="n">
         <v>4.1</v>
       </c>
-      <c r="H307" s="6" t="inlineStr"/>
-      <c r="I307" s="6" t="inlineStr"/>
-      <c r="J307" s="6" t="inlineStr"/>
-      <c r="K307" s="6" t="inlineStr"/>
+      <c r="H307" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I307" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J307" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K307" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
@@ -15523,10 +15533,20 @@
       <c r="G308" s="2" t="n">
         <v>3.6</v>
       </c>
-      <c r="H308" s="6" t="inlineStr"/>
-      <c r="I308" s="6" t="inlineStr"/>
-      <c r="J308" s="6" t="inlineStr"/>
-      <c r="K308" s="6" t="inlineStr"/>
+      <c r="H308" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I308" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J308" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K308" s="5" t="n">
+        <v>-260</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
@@ -15562,10 +15582,20 @@
       <c r="G309" s="2" t="n">
         <v>2.04</v>
       </c>
-      <c r="H309" s="6" t="inlineStr"/>
-      <c r="I309" s="6" t="inlineStr"/>
-      <c r="J309" s="6" t="inlineStr"/>
-      <c r="K309" s="6" t="inlineStr"/>
+      <c r="H309" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I309" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J309" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K309" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
@@ -20398,10 +20428,20 @@
       <c r="G433" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="H433" s="6" t="inlineStr"/>
-      <c r="I433" s="6" t="inlineStr"/>
-      <c r="J433" s="6" t="inlineStr"/>
-      <c r="K433" s="6" t="inlineStr"/>
+      <c r="H433" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I433" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J433" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K433" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" s="2" t="inlineStr">
@@ -20437,10 +20477,20 @@
       <c r="G434" s="2" t="n">
         <v>3.4</v>
       </c>
-      <c r="H434" s="6" t="inlineStr"/>
-      <c r="I434" s="6" t="inlineStr"/>
-      <c r="J434" s="6" t="inlineStr"/>
-      <c r="K434" s="6" t="inlineStr"/>
+      <c r="H434" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I434" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J434" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K434" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" s="2" t="inlineStr">
@@ -20476,10 +20526,20 @@
       <c r="G435" s="2" t="n">
         <v>2.4</v>
       </c>
-      <c r="H435" s="6" t="inlineStr"/>
-      <c r="I435" s="6" t="inlineStr"/>
-      <c r="J435" s="6" t="inlineStr"/>
-      <c r="K435" s="6" t="inlineStr"/>
+      <c r="H435" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I435" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J435" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K435" s="4" t="n">
+        <v>140</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" s="2" t="inlineStr">
@@ -20515,10 +20575,20 @@
       <c r="G436" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="H436" s="6" t="inlineStr"/>
-      <c r="I436" s="6" t="inlineStr"/>
-      <c r="J436" s="6" t="inlineStr"/>
-      <c r="K436" s="6" t="inlineStr"/>
+      <c r="H436" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I436" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J436" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K436" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" s="2" t="inlineStr">
@@ -20632,10 +20702,20 @@
       <c r="G439" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="H439" s="6" t="inlineStr"/>
-      <c r="I439" s="6" t="inlineStr"/>
-      <c r="J439" s="6" t="inlineStr"/>
-      <c r="K439" s="6" t="inlineStr"/>
+      <c r="H439" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I439" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J439" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K439" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" s="2" t="inlineStr">
@@ -20671,10 +20751,20 @@
       <c r="G440" s="2" t="n">
         <v>3.7</v>
       </c>
-      <c r="H440" s="6" t="inlineStr"/>
-      <c r="I440" s="6" t="inlineStr"/>
-      <c r="J440" s="6" t="inlineStr"/>
-      <c r="K440" s="6" t="inlineStr"/>
+      <c r="H440" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I440" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J440" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K440" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" s="2" t="inlineStr">
@@ -20710,10 +20800,20 @@
       <c r="G441" s="2" t="n">
         <v>2.22</v>
       </c>
-      <c r="H441" s="6" t="inlineStr"/>
-      <c r="I441" s="6" t="inlineStr"/>
-      <c r="J441" s="6" t="inlineStr"/>
-      <c r="K441" s="6" t="inlineStr"/>
+      <c r="H441" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I441" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J441" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K441" s="4" t="n">
+        <v>122</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" s="2" t="inlineStr">
@@ -20749,10 +20849,20 @@
       <c r="G442" s="2" t="n">
         <v>3.9</v>
       </c>
-      <c r="H442" s="6" t="inlineStr"/>
-      <c r="I442" s="6" t="inlineStr"/>
-      <c r="J442" s="6" t="inlineStr"/>
-      <c r="K442" s="6" t="inlineStr"/>
+      <c r="H442" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I442" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J442" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K442" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" s="2" t="inlineStr">
@@ -20788,10 +20898,20 @@
       <c r="G443" s="2" t="n">
         <v>3.75</v>
       </c>
-      <c r="H443" s="6" t="inlineStr"/>
-      <c r="I443" s="6" t="inlineStr"/>
-      <c r="J443" s="6" t="inlineStr"/>
-      <c r="K443" s="6" t="inlineStr"/>
+      <c r="H443" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I443" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J443" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K443" s="5" t="n">
+        <v>-275</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" s="2" t="inlineStr">
@@ -20827,10 +20947,20 @@
       <c r="G444" s="2" t="n">
         <v>2.36</v>
       </c>
-      <c r="H444" s="6" t="inlineStr"/>
-      <c r="I444" s="6" t="inlineStr"/>
-      <c r="J444" s="6" t="inlineStr"/>
-      <c r="K444" s="6" t="inlineStr"/>
+      <c r="H444" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I444" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J444" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K444" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" s="2" t="inlineStr">
@@ -20866,10 +20996,20 @@
       <c r="G445" s="2" t="n">
         <v>3.8</v>
       </c>
-      <c r="H445" s="6" t="inlineStr"/>
-      <c r="I445" s="6" t="inlineStr"/>
-      <c r="J445" s="6" t="inlineStr"/>
-      <c r="K445" s="6" t="inlineStr"/>
+      <c r="H445" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I445" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J445" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K445" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446" s="2" t="inlineStr">
@@ -20905,10 +21045,20 @@
       <c r="G446" s="2" t="n">
         <v>2.04</v>
       </c>
-      <c r="H446" s="6" t="inlineStr"/>
-      <c r="I446" s="6" t="inlineStr"/>
-      <c r="J446" s="6" t="inlineStr"/>
-      <c r="K446" s="6" t="inlineStr"/>
+      <c r="H446" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I446" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J446" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K446" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" s="2" t="inlineStr">
@@ -21334,10 +21484,20 @@
       <c r="G457" s="2" t="n">
         <v>4.1</v>
       </c>
-      <c r="H457" s="6" t="inlineStr"/>
-      <c r="I457" s="6" t="inlineStr"/>
-      <c r="J457" s="6" t="inlineStr"/>
-      <c r="K457" s="6" t="inlineStr"/>
+      <c r="H457" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I457" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J457" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K457" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" s="2" t="inlineStr">
@@ -21373,10 +21533,20 @@
       <c r="G458" s="2" t="n">
         <v>4.1</v>
       </c>
-      <c r="H458" s="6" t="inlineStr"/>
-      <c r="I458" s="6" t="inlineStr"/>
-      <c r="J458" s="6" t="inlineStr"/>
-      <c r="K458" s="6" t="inlineStr"/>
+      <c r="H458" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I458" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J458" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K458" s="5" t="n">
+        <v>-310</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459" s="2" t="inlineStr">
@@ -21412,10 +21582,20 @@
       <c r="G459" s="2" t="n">
         <v>4.5</v>
       </c>
-      <c r="H459" s="6" t="inlineStr"/>
-      <c r="I459" s="6" t="inlineStr"/>
-      <c r="J459" s="6" t="inlineStr"/>
-      <c r="K459" s="6" t="inlineStr"/>
+      <c r="H459" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I459" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J459" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K459" s="5" t="n">
+        <v>-350</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460" s="2" t="inlineStr">
@@ -21451,10 +21631,20 @@
       <c r="G460" s="2" t="n">
         <v>1.83</v>
       </c>
-      <c r="H460" s="6" t="inlineStr"/>
-      <c r="I460" s="6" t="inlineStr"/>
-      <c r="J460" s="6" t="inlineStr"/>
-      <c r="K460" s="6" t="inlineStr"/>
+      <c r="H460" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I460" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J460" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K460" s="4" t="n">
+        <v>83</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" s="2" t="inlineStr">
@@ -21646,10 +21836,20 @@
       <c r="G465" s="2" t="n">
         <v>3.75</v>
       </c>
-      <c r="H465" s="6" t="inlineStr"/>
-      <c r="I465" s="6" t="inlineStr"/>
-      <c r="J465" s="6" t="inlineStr"/>
-      <c r="K465" s="6" t="inlineStr"/>
+      <c r="H465" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I465" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J465" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K465" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" s="2" t="inlineStr">
@@ -21685,10 +21885,20 @@
       <c r="G466" s="2" t="n">
         <v>1.82</v>
       </c>
-      <c r="H466" s="6" t="inlineStr"/>
-      <c r="I466" s="6" t="inlineStr"/>
-      <c r="J466" s="6" t="inlineStr"/>
-      <c r="K466" s="6" t="inlineStr"/>
+      <c r="H466" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I466" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J466" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K466" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467" s="2" t="inlineStr">
@@ -21724,10 +21934,20 @@
       <c r="G467" s="2" t="n">
         <v>1.87</v>
       </c>
-      <c r="H467" s="6" t="inlineStr"/>
-      <c r="I467" s="6" t="inlineStr"/>
-      <c r="J467" s="6" t="inlineStr"/>
-      <c r="K467" s="6" t="inlineStr"/>
+      <c r="H467" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I467" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J467" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K467" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="468">
       <c r="A468" s="2" t="inlineStr">
@@ -21841,10 +22061,20 @@
       <c r="G470" s="2" t="n">
         <v>4.1</v>
       </c>
-      <c r="H470" s="6" t="inlineStr"/>
-      <c r="I470" s="6" t="inlineStr"/>
-      <c r="J470" s="6" t="inlineStr"/>
-      <c r="K470" s="6" t="inlineStr"/>
+      <c r="H470" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I470" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J470" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K470" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471" s="2" t="inlineStr">
@@ -21880,10 +22110,20 @@
       <c r="G471" s="2" t="n">
         <v>4.3</v>
       </c>
-      <c r="H471" s="6" t="inlineStr"/>
-      <c r="I471" s="6" t="inlineStr"/>
-      <c r="J471" s="6" t="inlineStr"/>
-      <c r="K471" s="6" t="inlineStr"/>
+      <c r="H471" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I471" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J471" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K471" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472" s="2" t="inlineStr">
@@ -21997,10 +22237,20 @@
       <c r="G474" s="2" t="n">
         <v>4.1</v>
       </c>
-      <c r="H474" s="6" t="inlineStr"/>
-      <c r="I474" s="6" t="inlineStr"/>
-      <c r="J474" s="6" t="inlineStr"/>
-      <c r="K474" s="6" t="inlineStr"/>
+      <c r="H474" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I474" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J474" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K474" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" s="2" t="inlineStr">
@@ -22114,10 +22364,20 @@
       <c r="G477" s="2" t="n">
         <v>3.7</v>
       </c>
-      <c r="H477" s="6" t="inlineStr"/>
-      <c r="I477" s="6" t="inlineStr"/>
-      <c r="J477" s="6" t="inlineStr"/>
-      <c r="K477" s="6" t="inlineStr"/>
+      <c r="H477" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I477" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J477" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K477" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478" s="2" t="inlineStr">
@@ -22153,10 +22413,20 @@
       <c r="G478" s="2" t="n">
         <v>1.81</v>
       </c>
-      <c r="H478" s="6" t="inlineStr"/>
-      <c r="I478" s="6" t="inlineStr"/>
-      <c r="J478" s="6" t="inlineStr"/>
-      <c r="K478" s="6" t="inlineStr"/>
+      <c r="H478" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I478" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J478" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K478" s="4" t="n">
+        <v>81</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" s="2" t="inlineStr">
@@ -22426,10 +22696,20 @@
       <c r="G485" s="2" t="n">
         <v>3.7</v>
       </c>
-      <c r="H485" s="6" t="inlineStr"/>
-      <c r="I485" s="6" t="inlineStr"/>
-      <c r="J485" s="6" t="inlineStr"/>
-      <c r="K485" s="6" t="inlineStr"/>
+      <c r="H485" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I485" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J485" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K485" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="486">
       <c r="A486" s="2" t="inlineStr">
@@ -22465,10 +22745,20 @@
       <c r="G486" s="2" t="n">
         <v>3.9</v>
       </c>
-      <c r="H486" s="6" t="inlineStr"/>
-      <c r="I486" s="6" t="inlineStr"/>
-      <c r="J486" s="6" t="inlineStr"/>
-      <c r="K486" s="6" t="inlineStr"/>
+      <c r="H486" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I486" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J486" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K486" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="487">
       <c r="A487" s="2" t="inlineStr">
@@ -22504,10 +22794,20 @@
       <c r="G487" s="2" t="n">
         <v>3.8</v>
       </c>
-      <c r="H487" s="6" t="inlineStr"/>
-      <c r="I487" s="6" t="inlineStr"/>
-      <c r="J487" s="6" t="inlineStr"/>
-      <c r="K487" s="6" t="inlineStr"/>
+      <c r="H487" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I487" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J487" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K487" s="5" t="n">
+        <v>-280</v>
+      </c>
     </row>
     <row r="488">
       <c r="A488" s="2" t="inlineStr">
@@ -22543,10 +22843,20 @@
       <c r="G488" s="2" t="n">
         <v>1.8</v>
       </c>
-      <c r="H488" s="6" t="inlineStr"/>
-      <c r="I488" s="6" t="inlineStr"/>
-      <c r="J488" s="6" t="inlineStr"/>
-      <c r="K488" s="6" t="inlineStr"/>
+      <c r="H488" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I488" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J488" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K488" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" s="2" t="inlineStr">
@@ -22582,10 +22892,20 @@
       <c r="G489" s="2" t="n">
         <v>3.55</v>
       </c>
-      <c r="H489" s="6" t="inlineStr"/>
-      <c r="I489" s="6" t="inlineStr"/>
-      <c r="J489" s="6" t="inlineStr"/>
-      <c r="K489" s="6" t="inlineStr"/>
+      <c r="H489" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I489" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J489" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K489" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="490">
       <c r="A490" s="2" t="inlineStr">
@@ -22621,10 +22941,20 @@
       <c r="G490" s="2" t="n">
         <v>1.86</v>
       </c>
-      <c r="H490" s="6" t="inlineStr"/>
-      <c r="I490" s="6" t="inlineStr"/>
-      <c r="J490" s="6" t="inlineStr"/>
-      <c r="K490" s="6" t="inlineStr"/>
+      <c r="H490" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I490" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J490" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K490" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" s="2" t="inlineStr">
@@ -22660,10 +22990,20 @@
       <c r="G491" s="2" t="n">
         <v>1.83</v>
       </c>
-      <c r="H491" s="6" t="inlineStr"/>
-      <c r="I491" s="6" t="inlineStr"/>
-      <c r="J491" s="6" t="inlineStr"/>
-      <c r="K491" s="6" t="inlineStr"/>
+      <c r="H491" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I491" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J491" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K491" s="4" t="n">
+        <v>83</v>
+      </c>
     </row>
     <row r="492">
       <c r="A492" s="2" t="inlineStr">
@@ -22699,10 +23039,20 @@
       <c r="G492" s="2" t="n">
         <v>2.28</v>
       </c>
-      <c r="H492" s="6" t="inlineStr"/>
-      <c r="I492" s="6" t="inlineStr"/>
-      <c r="J492" s="6" t="inlineStr"/>
-      <c r="K492" s="6" t="inlineStr"/>
+      <c r="H492" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I492" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J492" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K492" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493" s="2" t="inlineStr">
@@ -22738,10 +23088,20 @@
       <c r="G493" s="2" t="n">
         <v>3.6</v>
       </c>
-      <c r="H493" s="6" t="inlineStr"/>
-      <c r="I493" s="6" t="inlineStr"/>
-      <c r="J493" s="6" t="inlineStr"/>
-      <c r="K493" s="6" t="inlineStr"/>
+      <c r="H493" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I493" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J493" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K493" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="494">
       <c r="A494" s="2" t="inlineStr">
@@ -22777,10 +23137,20 @@
       <c r="G494" s="2" t="n">
         <v>2.16</v>
       </c>
-      <c r="H494" s="6" t="inlineStr"/>
-      <c r="I494" s="6" t="inlineStr"/>
-      <c r="J494" s="6" t="inlineStr"/>
-      <c r="K494" s="6" t="inlineStr"/>
+      <c r="H494" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I494" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J494" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K494" s="4" t="n">
+        <v>116</v>
+      </c>
     </row>
     <row r="495">
       <c r="A495" s="2" t="inlineStr">
@@ -22855,10 +23225,20 @@
       <c r="G496" s="2" t="n">
         <v>2.34</v>
       </c>
-      <c r="H496" s="6" t="inlineStr"/>
-      <c r="I496" s="6" t="inlineStr"/>
-      <c r="J496" s="6" t="inlineStr"/>
-      <c r="K496" s="6" t="inlineStr"/>
+      <c r="H496" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I496" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J496" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K496" s="4" t="n">
+        <v>134</v>
+      </c>
     </row>
     <row r="497">
       <c r="A497" s="2" t="inlineStr">
@@ -22894,10 +23274,20 @@
       <c r="G497" s="2" t="n">
         <v>1.98</v>
       </c>
-      <c r="H497" s="6" t="inlineStr"/>
-      <c r="I497" s="6" t="inlineStr"/>
-      <c r="J497" s="6" t="inlineStr"/>
-      <c r="K497" s="6" t="inlineStr"/>
+      <c r="H497" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I497" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J497" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K497" s="4" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="498">
       <c r="A498" s="2" t="inlineStr">
@@ -22933,10 +23323,20 @@
       <c r="G498" s="2" t="n">
         <v>3.65</v>
       </c>
-      <c r="H498" s="6" t="inlineStr"/>
-      <c r="I498" s="6" t="inlineStr"/>
-      <c r="J498" s="6" t="inlineStr"/>
-      <c r="K498" s="6" t="inlineStr"/>
+      <c r="H498" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I498" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J498" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K498" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="499">
       <c r="A499" s="2" t="inlineStr">
@@ -22972,10 +23372,20 @@
       <c r="G499" s="2" t="n">
         <v>2.02</v>
       </c>
-      <c r="H499" s="6" t="inlineStr"/>
-      <c r="I499" s="6" t="inlineStr"/>
-      <c r="J499" s="6" t="inlineStr"/>
-      <c r="K499" s="6" t="inlineStr"/>
+      <c r="H499" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I499" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J499" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K499" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500" s="2" t="inlineStr">
@@ -23011,10 +23421,20 @@
       <c r="G500" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="H500" s="6" t="inlineStr"/>
-      <c r="I500" s="6" t="inlineStr"/>
-      <c r="J500" s="6" t="inlineStr"/>
-      <c r="K500" s="6" t="inlineStr"/>
+      <c r="H500" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I500" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J500" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K500" s="5" t="n">
+        <v>-1000</v>
+      </c>
     </row>
     <row r="501">
       <c r="A501" s="2" t="inlineStr">
@@ -23050,10 +23470,20 @@
       <c r="G501" s="2" t="n">
         <v>3.4</v>
       </c>
-      <c r="H501" s="6" t="inlineStr"/>
-      <c r="I501" s="6" t="inlineStr"/>
-      <c r="J501" s="6" t="inlineStr"/>
-      <c r="K501" s="6" t="inlineStr"/>
+      <c r="H501" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I501" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J501" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K501" s="5" t="n">
+        <v>-240</v>
+      </c>
     </row>
     <row r="502">
       <c r="A502" s="2" t="inlineStr">
@@ -23089,10 +23519,20 @@
       <c r="G502" s="2" t="n">
         <v>2.28</v>
       </c>
-      <c r="H502" s="6" t="inlineStr"/>
-      <c r="I502" s="6" t="inlineStr"/>
-      <c r="J502" s="6" t="inlineStr"/>
-      <c r="K502" s="6" t="inlineStr"/>
+      <c r="H502" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I502" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J502" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K502" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="503">
       <c r="A503" s="2" t="inlineStr">
@@ -23128,10 +23568,20 @@
       <c r="G503" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H503" s="6" t="inlineStr"/>
-      <c r="I503" s="6" t="inlineStr"/>
-      <c r="J503" s="6" t="inlineStr"/>
-      <c r="K503" s="6" t="inlineStr"/>
+      <c r="H503" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I503" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J503" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K503" s="4" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="504">
       <c r="A504" s="2" t="inlineStr">
@@ -23167,10 +23617,20 @@
       <c r="G504" s="2" t="n">
         <v>3.85</v>
       </c>
-      <c r="H504" s="6" t="inlineStr"/>
-      <c r="I504" s="6" t="inlineStr"/>
-      <c r="J504" s="6" t="inlineStr"/>
-      <c r="K504" s="6" t="inlineStr"/>
+      <c r="H504" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I504" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J504" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K504" s="5" t="n">
+        <v>-285</v>
+      </c>
     </row>
     <row r="505">
       <c r="A505" s="2" t="inlineStr">
@@ -23206,10 +23666,20 @@
       <c r="G505" s="2" t="n">
         <v>1.95</v>
       </c>
-      <c r="H505" s="6" t="inlineStr"/>
-      <c r="I505" s="6" t="inlineStr"/>
-      <c r="J505" s="6" t="inlineStr"/>
-      <c r="K505" s="6" t="inlineStr"/>
+      <c r="H505" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I505" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J505" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K505" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="506">
       <c r="A506" s="2" t="inlineStr">
@@ -23245,10 +23715,20 @@
       <c r="G506" s="2" t="n">
         <v>3.65</v>
       </c>
-      <c r="H506" s="6" t="inlineStr"/>
-      <c r="I506" s="6" t="inlineStr"/>
-      <c r="J506" s="6" t="inlineStr"/>
-      <c r="K506" s="6" t="inlineStr"/>
+      <c r="H506" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I506" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J506" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K506" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="507">
       <c r="A507" s="2" t="inlineStr">
@@ -23284,10 +23764,20 @@
       <c r="G507" s="2" t="n">
         <v>1.93</v>
       </c>
-      <c r="H507" s="6" t="inlineStr"/>
-      <c r="I507" s="6" t="inlineStr"/>
-      <c r="J507" s="6" t="inlineStr"/>
-      <c r="K507" s="6" t="inlineStr"/>
+      <c r="H507" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I507" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J507" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K507" s="4" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="508">
       <c r="A508" s="2" t="inlineStr">
@@ -23362,10 +23852,20 @@
       <c r="G509" s="2" t="n">
         <v>1.84</v>
       </c>
-      <c r="H509" s="6" t="inlineStr"/>
-      <c r="I509" s="6" t="inlineStr"/>
-      <c r="J509" s="6" t="inlineStr"/>
-      <c r="K509" s="6" t="inlineStr"/>
+      <c r="H509" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I509" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J509" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K509" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="510">
       <c r="A510" s="2" t="inlineStr">
@@ -23401,10 +23901,20 @@
       <c r="G510" s="2" t="n">
         <v>3.55</v>
       </c>
-      <c r="H510" s="6" t="inlineStr"/>
-      <c r="I510" s="6" t="inlineStr"/>
-      <c r="J510" s="6" t="inlineStr"/>
-      <c r="K510" s="6" t="inlineStr"/>
+      <c r="H510" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I510" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J510" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K510" s="5" t="n">
+        <v>-255</v>
+      </c>
     </row>
     <row r="511">
       <c r="A511" s="2" t="inlineStr">
@@ -23440,10 +23950,20 @@
       <c r="G511" s="2" t="n">
         <v>2.06</v>
       </c>
-      <c r="H511" s="6" t="inlineStr"/>
-      <c r="I511" s="6" t="inlineStr"/>
-      <c r="J511" s="6" t="inlineStr"/>
-      <c r="K511" s="6" t="inlineStr"/>
+      <c r="H511" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I511" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J511" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K511" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="512">
       <c r="A512" s="2" t="inlineStr">
@@ -23479,10 +23999,20 @@
       <c r="G512" s="2" t="n">
         <v>3.75</v>
       </c>
-      <c r="H512" s="6" t="inlineStr"/>
-      <c r="I512" s="6" t="inlineStr"/>
-      <c r="J512" s="6" t="inlineStr"/>
-      <c r="K512" s="6" t="inlineStr"/>
+      <c r="H512" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I512" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J512" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K512" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="513">
       <c r="A513" s="2" t="inlineStr">
@@ -23518,10 +24048,20 @@
       <c r="G513" s="2" t="n">
         <v>1.85</v>
       </c>
-      <c r="H513" s="6" t="inlineStr"/>
-      <c r="I513" s="6" t="inlineStr"/>
-      <c r="J513" s="6" t="inlineStr"/>
-      <c r="K513" s="6" t="inlineStr"/>
+      <c r="H513" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I513" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J513" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K513" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="514">
       <c r="A514" s="2" t="inlineStr">
@@ -23557,10 +24097,20 @@
       <c r="G514" s="2" t="n">
         <v>1.91</v>
       </c>
-      <c r="H514" s="6" t="inlineStr"/>
-      <c r="I514" s="6" t="inlineStr"/>
-      <c r="J514" s="6" t="inlineStr"/>
-      <c r="K514" s="6" t="inlineStr"/>
+      <c r="H514" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I514" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J514" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K514" s="4" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="515">
       <c r="A515" s="2" t="inlineStr">
@@ -23596,10 +24146,20 @@
       <c r="G515" s="2" t="n">
         <v>2.84</v>
       </c>
-      <c r="H515" s="6" t="inlineStr"/>
-      <c r="I515" s="6" t="inlineStr"/>
-      <c r="J515" s="6" t="inlineStr"/>
-      <c r="K515" s="6" t="inlineStr"/>
+      <c r="H515" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I515" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J515" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K515" s="5" t="n">
+        <v>-184</v>
+      </c>
     </row>
     <row r="516">
       <c r="A516" s="2" t="inlineStr">
@@ -23635,10 +24195,20 @@
       <c r="G516" s="2" t="n">
         <v>3.9</v>
       </c>
-      <c r="H516" s="6" t="inlineStr"/>
-      <c r="I516" s="6" t="inlineStr"/>
-      <c r="J516" s="6" t="inlineStr"/>
-      <c r="K516" s="6" t="inlineStr"/>
+      <c r="H516" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I516" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J516" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K516" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="517">
       <c r="A517" s="2" t="inlineStr">
@@ -23674,10 +24244,20 @@
       <c r="G517" s="2" t="n">
         <v>1.86</v>
       </c>
-      <c r="H517" s="6" t="inlineStr"/>
-      <c r="I517" s="6" t="inlineStr"/>
-      <c r="J517" s="6" t="inlineStr"/>
-      <c r="K517" s="6" t="inlineStr"/>
+      <c r="H517" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I517" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J517" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K517" s="4" t="n">
+        <v>86</v>
+      </c>
     </row>
     <row r="518">
       <c r="A518" s="2" t="inlineStr">
@@ -23713,10 +24293,20 @@
       <c r="G518" s="2" t="n">
         <v>4.1</v>
       </c>
-      <c r="H518" s="6" t="inlineStr"/>
-      <c r="I518" s="6" t="inlineStr"/>
-      <c r="J518" s="6" t="inlineStr"/>
-      <c r="K518" s="6" t="inlineStr"/>
+      <c r="H518" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I518" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J518" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K518" s="5" t="n">
+        <v>-310</v>
+      </c>
     </row>
     <row r="519">
       <c r="A519" s="2" t="inlineStr">
@@ -23752,10 +24342,20 @@
       <c r="G519" s="2" t="n">
         <v>3.8</v>
       </c>
-      <c r="H519" s="6" t="inlineStr"/>
-      <c r="I519" s="6" t="inlineStr"/>
-      <c r="J519" s="6" t="inlineStr"/>
-      <c r="K519" s="6" t="inlineStr"/>
+      <c r="H519" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I519" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J519" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K519" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="520">
       <c r="A520" s="2" t="inlineStr">
@@ -23791,10 +24391,20 @@
       <c r="G520" s="2" t="n">
         <v>1.82</v>
       </c>
-      <c r="H520" s="6" t="inlineStr"/>
-      <c r="I520" s="6" t="inlineStr"/>
-      <c r="J520" s="6" t="inlineStr"/>
-      <c r="K520" s="6" t="inlineStr"/>
+      <c r="H520" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I520" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J520" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K520" s="4" t="n">
+        <v>82</v>
+      </c>
     </row>
     <row r="521">
       <c r="A521" s="2" t="inlineStr">
@@ -23869,10 +24479,20 @@
       <c r="G522" s="2" t="n">
         <v>4.2</v>
       </c>
-      <c r="H522" s="6" t="inlineStr"/>
-      <c r="I522" s="6" t="inlineStr"/>
-      <c r="J522" s="6" t="inlineStr"/>
-      <c r="K522" s="6" t="inlineStr"/>
+      <c r="H522" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I522" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J522" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K522" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="523">
       <c r="A523" s="2" t="inlineStr">
@@ -23986,10 +24606,20 @@
       <c r="G525" s="2" t="n">
         <v>2.56</v>
       </c>
-      <c r="H525" s="6" t="inlineStr"/>
-      <c r="I525" s="6" t="inlineStr"/>
-      <c r="J525" s="6" t="inlineStr"/>
-      <c r="K525" s="6" t="inlineStr"/>
+      <c r="H525" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I525" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J525" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K525" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="526">
       <c r="A526" s="2" t="inlineStr">
@@ -24025,10 +24655,20 @@
       <c r="G526" s="2" t="n">
         <v>3.15</v>
       </c>
-      <c r="H526" s="6" t="inlineStr"/>
-      <c r="I526" s="6" t="inlineStr"/>
-      <c r="J526" s="6" t="inlineStr"/>
-      <c r="K526" s="6" t="inlineStr"/>
+      <c r="H526" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I526" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J526" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K526" s="5" t="n">
+        <v>-215</v>
+      </c>
     </row>
     <row r="527">
       <c r="A527" s="2" t="inlineStr">
@@ -24064,10 +24704,20 @@
       <c r="G527" s="2" t="n">
         <v>3.9</v>
       </c>
-      <c r="H527" s="6" t="inlineStr"/>
-      <c r="I527" s="6" t="inlineStr"/>
-      <c r="J527" s="6" t="inlineStr"/>
-      <c r="K527" s="6" t="inlineStr"/>
+      <c r="H527" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I527" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J527" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K527" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="528">
       <c r="A528" s="2" t="inlineStr">
@@ -24259,10 +24909,20 @@
       <c r="G532" s="2" t="n">
         <v>9.6</v>
       </c>
-      <c r="H532" s="6" t="inlineStr"/>
-      <c r="I532" s="6" t="inlineStr"/>
-      <c r="J532" s="6" t="inlineStr"/>
-      <c r="K532" s="6" t="inlineStr"/>
+      <c r="H532" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I532" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J532" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K532" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="533">
       <c r="A533" s="2" t="inlineStr">
@@ -24298,10 +24958,20 @@
       <c r="G533" s="2" t="n">
         <v>3.35</v>
       </c>
-      <c r="H533" s="6" t="inlineStr"/>
-      <c r="I533" s="6" t="inlineStr"/>
-      <c r="J533" s="6" t="inlineStr"/>
-      <c r="K533" s="6" t="inlineStr"/>
+      <c r="H533" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I533" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J533" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K533" s="5" t="n">
+        <v>-235</v>
+      </c>
     </row>
     <row r="534">
       <c r="A534" s="2" t="inlineStr">
@@ -24337,10 +25007,20 @@
       <c r="G534" s="2" t="n">
         <v>2.54</v>
       </c>
-      <c r="H534" s="6" t="inlineStr"/>
-      <c r="I534" s="6" t="inlineStr"/>
-      <c r="J534" s="6" t="inlineStr"/>
-      <c r="K534" s="6" t="inlineStr"/>
+      <c r="H534" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I534" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J534" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K534" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="535">
       <c r="A535" s="2" t="inlineStr">
@@ -24376,10 +25056,20 @@
       <c r="G535" s="2" t="n">
         <v>9.4</v>
       </c>
-      <c r="H535" s="6" t="inlineStr"/>
-      <c r="I535" s="6" t="inlineStr"/>
-      <c r="J535" s="6" t="inlineStr"/>
-      <c r="K535" s="6" t="inlineStr"/>
+      <c r="H535" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I535" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J535" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K535" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="536">
       <c r="A536" s="2" t="inlineStr">
@@ -24415,10 +25105,20 @@
       <c r="G536" s="2" t="n">
         <v>4.2</v>
       </c>
-      <c r="H536" s="6" t="inlineStr"/>
-      <c r="I536" s="6" t="inlineStr"/>
-      <c r="J536" s="6" t="inlineStr"/>
-      <c r="K536" s="6" t="inlineStr"/>
+      <c r="H536" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I536" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J536" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K536" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="537">
       <c r="A537" s="2" t="inlineStr">
@@ -24454,10 +25154,20 @@
       <c r="G537" s="2" t="n">
         <v>2.86</v>
       </c>
-      <c r="H537" s="6" t="inlineStr"/>
-      <c r="I537" s="6" t="inlineStr"/>
-      <c r="J537" s="6" t="inlineStr"/>
-      <c r="K537" s="6" t="inlineStr"/>
+      <c r="H537" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I537" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J537" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K537" s="5" t="n">
+        <v>-186</v>
+      </c>
     </row>
     <row r="538">
       <c r="A538" s="2" t="inlineStr">
@@ -24493,10 +25203,20 @@
       <c r="G538" s="2" t="n">
         <v>10.5</v>
       </c>
-      <c r="H538" s="6" t="inlineStr"/>
-      <c r="I538" s="6" t="inlineStr"/>
-      <c r="J538" s="6" t="inlineStr"/>
-      <c r="K538" s="6" t="inlineStr"/>
+      <c r="H538" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I538" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J538" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K538" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="539">
       <c r="A539" s="2" t="inlineStr">
@@ -24532,10 +25252,20 @@
       <c r="G539" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="H539" s="6" t="inlineStr"/>
-      <c r="I539" s="6" t="inlineStr"/>
-      <c r="J539" s="6" t="inlineStr"/>
-      <c r="K539" s="6" t="inlineStr"/>
+      <c r="H539" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I539" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J539" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K539" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="540">
       <c r="A540" s="2" t="inlineStr">
@@ -24571,10 +25301,20 @@
       <c r="G540" s="2" t="n">
         <v>2.34</v>
       </c>
-      <c r="H540" s="6" t="inlineStr"/>
-      <c r="I540" s="6" t="inlineStr"/>
-      <c r="J540" s="6" t="inlineStr"/>
-      <c r="K540" s="6" t="inlineStr"/>
+      <c r="H540" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I540" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J540" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K540" s="4" t="n">
+        <v>134</v>
+      </c>
     </row>
     <row r="541">
       <c r="A541" s="2" t="inlineStr">
@@ -24727,10 +25467,20 @@
       <c r="G544" s="2" t="n">
         <v>2.04</v>
       </c>
-      <c r="H544" s="6" t="inlineStr"/>
-      <c r="I544" s="6" t="inlineStr"/>
-      <c r="J544" s="6" t="inlineStr"/>
-      <c r="K544" s="6" t="inlineStr"/>
+      <c r="H544" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I544" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J544" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K544" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="545">
       <c r="A545" s="2" t="inlineStr">
@@ -24766,10 +25516,20 @@
       <c r="G545" s="2" t="n">
         <v>2.38</v>
       </c>
-      <c r="H545" s="6" t="inlineStr"/>
-      <c r="I545" s="6" t="inlineStr"/>
-      <c r="J545" s="6" t="inlineStr"/>
-      <c r="K545" s="6" t="inlineStr"/>
+      <c r="H545" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I545" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J545" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K545" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="546">
       <c r="A546" s="2" t="inlineStr">
@@ -24961,10 +25721,20 @@
       <c r="G550" s="2" t="n">
         <v>10.5</v>
       </c>
-      <c r="H550" s="6" t="inlineStr"/>
-      <c r="I550" s="6" t="inlineStr"/>
-      <c r="J550" s="6" t="inlineStr"/>
-      <c r="K550" s="6" t="inlineStr"/>
+      <c r="H550" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I550" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J550" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K550" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="551">
       <c r="A551" s="2" t="inlineStr">
@@ -25000,10 +25770,20 @@
       <c r="G551" s="2" t="n">
         <v>2.4</v>
       </c>
-      <c r="H551" s="6" t="inlineStr"/>
-      <c r="I551" s="6" t="inlineStr"/>
-      <c r="J551" s="6" t="inlineStr"/>
-      <c r="K551" s="6" t="inlineStr"/>
+      <c r="H551" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I551" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J551" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K551" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="552">
       <c r="A552" s="2" t="inlineStr">
@@ -25039,10 +25819,20 @@
       <c r="G552" s="2" t="n">
         <v>2.2</v>
       </c>
-      <c r="H552" s="6" t="inlineStr"/>
-      <c r="I552" s="6" t="inlineStr"/>
-      <c r="J552" s="6" t="inlineStr"/>
-      <c r="K552" s="6" t="inlineStr"/>
+      <c r="H552" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I552" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J552" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K552" s="5" t="n">
+        <v>-120</v>
+      </c>
     </row>
     <row r="553">
       <c r="A553" s="2" t="inlineStr">
@@ -25234,10 +26024,20 @@
       <c r="G557" s="2" t="n">
         <v>3.45</v>
       </c>
-      <c r="H557" s="6" t="inlineStr"/>
-      <c r="I557" s="6" t="inlineStr"/>
-      <c r="J557" s="6" t="inlineStr"/>
-      <c r="K557" s="6" t="inlineStr"/>
+      <c r="H557" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I557" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J557" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K557" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="558">
       <c r="A558" s="2" t="inlineStr">
@@ -25273,10 +26073,20 @@
       <c r="G558" s="2" t="n">
         <v>2.24</v>
       </c>
-      <c r="H558" s="6" t="inlineStr"/>
-      <c r="I558" s="6" t="inlineStr"/>
-      <c r="J558" s="6" t="inlineStr"/>
-      <c r="K558" s="6" t="inlineStr"/>
+      <c r="H558" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I558" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J558" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K558" s="4" t="n">
+        <v>124</v>
+      </c>
     </row>
     <row r="559">
       <c r="A559" s="2" t="inlineStr">
@@ -26287,10 +27097,20 @@
       <c r="G584" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="H584" s="6" t="inlineStr"/>
-      <c r="I584" s="6" t="inlineStr"/>
-      <c r="J584" s="6" t="inlineStr"/>
-      <c r="K584" s="6" t="inlineStr"/>
+      <c r="H584" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I584" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J584" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K584" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="585">
       <c r="A585" s="2" t="inlineStr">
@@ -26326,10 +27146,20 @@
       <c r="G585" s="2" t="n">
         <v>2.18</v>
       </c>
-      <c r="H585" s="6" t="inlineStr"/>
-      <c r="I585" s="6" t="inlineStr"/>
-      <c r="J585" s="6" t="inlineStr"/>
-      <c r="K585" s="6" t="inlineStr"/>
+      <c r="H585" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I585" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J585" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K585" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="586">
       <c r="A586" s="2" t="inlineStr">
@@ -26365,10 +27195,20 @@
       <c r="G586" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="H586" s="6" t="inlineStr"/>
-      <c r="I586" s="6" t="inlineStr"/>
-      <c r="J586" s="6" t="inlineStr"/>
-      <c r="K586" s="6" t="inlineStr"/>
+      <c r="H586" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I586" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J586" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K586" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="587">
       <c r="A587" s="2" t="inlineStr">
@@ -26404,10 +27244,20 @@
       <c r="G587" s="2" t="n">
         <v>1.87</v>
       </c>
-      <c r="H587" s="6" t="inlineStr"/>
-      <c r="I587" s="6" t="inlineStr"/>
-      <c r="J587" s="6" t="inlineStr"/>
-      <c r="K587" s="6" t="inlineStr"/>
+      <c r="H587" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I587" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J587" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K587" s="4" t="n">
+        <v>87</v>
+      </c>
     </row>
     <row r="588">
       <c r="A588" s="2" t="inlineStr">
@@ -26677,10 +27527,20 @@
       <c r="G594" s="2" t="n">
         <v>4.3</v>
       </c>
-      <c r="H594" s="6" t="inlineStr"/>
-      <c r="I594" s="6" t="inlineStr"/>
-      <c r="J594" s="6" t="inlineStr"/>
-      <c r="K594" s="6" t="inlineStr"/>
+      <c r="H594" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I594" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J594" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K594" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="595">
       <c r="A595" s="2" t="inlineStr">
@@ -26716,10 +27576,20 @@
       <c r="G595" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H595" s="6" t="inlineStr"/>
-      <c r="I595" s="6" t="inlineStr"/>
-      <c r="J595" s="6" t="inlineStr"/>
-      <c r="K595" s="6" t="inlineStr"/>
+      <c r="H595" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I595" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J595" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K595" s="4" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="596">
       <c r="A596" s="2" t="inlineStr">
@@ -26755,10 +27625,20 @@
       <c r="G596" s="2" t="n">
         <v>4.1</v>
       </c>
-      <c r="H596" s="6" t="inlineStr"/>
-      <c r="I596" s="6" t="inlineStr"/>
-      <c r="J596" s="6" t="inlineStr"/>
-      <c r="K596" s="6" t="inlineStr"/>
+      <c r="H596" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I596" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J596" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K596" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="597">
       <c r="A597" s="2" t="inlineStr">
@@ -26794,10 +27674,20 @@
       <c r="G597" s="2" t="n">
         <v>1.94</v>
       </c>
-      <c r="H597" s="6" t="inlineStr"/>
-      <c r="I597" s="6" t="inlineStr"/>
-      <c r="J597" s="6" t="inlineStr"/>
-      <c r="K597" s="6" t="inlineStr"/>
+      <c r="H597" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I597" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J597" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K597" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="598">
       <c r="A598" s="2" t="inlineStr">
@@ -26833,10 +27723,20 @@
       <c r="G598" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="H598" s="6" t="inlineStr"/>
-      <c r="I598" s="6" t="inlineStr"/>
-      <c r="J598" s="6" t="inlineStr"/>
-      <c r="K598" s="6" t="inlineStr"/>
+      <c r="H598" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I598" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J598" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K598" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="599">
       <c r="A599" s="2" t="inlineStr">
@@ -26872,10 +27772,20 @@
       <c r="G599" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="H599" s="6" t="inlineStr"/>
-      <c r="I599" s="6" t="inlineStr"/>
-      <c r="J599" s="6" t="inlineStr"/>
-      <c r="K599" s="6" t="inlineStr"/>
+      <c r="H599" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I599" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J599" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K599" s="5" t="n">
+        <v>-250</v>
+      </c>
     </row>
     <row r="600">
       <c r="A600" s="2" t="inlineStr">
@@ -26911,10 +27821,20 @@
       <c r="G600" s="2" t="n">
         <v>2.18</v>
       </c>
-      <c r="H600" s="6" t="inlineStr"/>
-      <c r="I600" s="6" t="inlineStr"/>
-      <c r="J600" s="6" t="inlineStr"/>
-      <c r="K600" s="6" t="inlineStr"/>
+      <c r="H600" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I600" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J600" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K600" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="601">
       <c r="A601" s="2" t="inlineStr">
@@ -26950,10 +27870,20 @@
       <c r="G601" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="H601" s="6" t="inlineStr"/>
-      <c r="I601" s="6" t="inlineStr"/>
-      <c r="J601" s="6" t="inlineStr"/>
-      <c r="K601" s="6" t="inlineStr"/>
+      <c r="H601" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I601" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J601" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K601" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="602">
       <c r="A602" s="2" t="inlineStr">
@@ -26989,10 +27919,20 @@
       <c r="G602" s="2" t="n">
         <v>2.42</v>
       </c>
-      <c r="H602" s="6" t="inlineStr"/>
-      <c r="I602" s="6" t="inlineStr"/>
-      <c r="J602" s="6" t="inlineStr"/>
-      <c r="K602" s="6" t="inlineStr"/>
+      <c r="H602" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I602" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J602" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K602" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="603">
       <c r="A603" s="2" t="inlineStr">
@@ -27028,10 +27968,20 @@
       <c r="G603" s="2" t="n">
         <v>3.7</v>
       </c>
-      <c r="H603" s="6" t="inlineStr"/>
-      <c r="I603" s="6" t="inlineStr"/>
-      <c r="J603" s="6" t="inlineStr"/>
-      <c r="K603" s="6" t="inlineStr"/>
+      <c r="H603" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I603" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J603" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K603" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="604">
       <c r="A604" s="2" t="inlineStr">
@@ -27067,10 +28017,20 @@
       <c r="G604" s="2" t="n">
         <v>1.96</v>
       </c>
-      <c r="H604" s="6" t="inlineStr"/>
-      <c r="I604" s="6" t="inlineStr"/>
-      <c r="J604" s="6" t="inlineStr"/>
-      <c r="K604" s="6" t="inlineStr"/>
+      <c r="H604" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I604" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J604" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K604" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="605">
       <c r="A605" s="2" t="inlineStr">
@@ -27106,10 +28066,20 @@
       <c r="G605" s="2" t="n">
         <v>3.45</v>
       </c>
-      <c r="H605" s="6" t="inlineStr"/>
-      <c r="I605" s="6" t="inlineStr"/>
-      <c r="J605" s="6" t="inlineStr"/>
-      <c r="K605" s="6" t="inlineStr"/>
+      <c r="H605" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I605" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J605" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K605" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="606">
       <c r="A606" s="2" t="inlineStr">
@@ -27145,10 +28115,20 @@
       <c r="G606" s="2" t="n">
         <v>2.12</v>
       </c>
-      <c r="H606" s="6" t="inlineStr"/>
-      <c r="I606" s="6" t="inlineStr"/>
-      <c r="J606" s="6" t="inlineStr"/>
-      <c r="K606" s="6" t="inlineStr"/>
+      <c r="H606" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I606" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J606" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K606" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="607">
       <c r="A607" s="2" t="inlineStr">
@@ -27184,10 +28164,20 @@
       <c r="G607" s="2" t="n">
         <v>11.5</v>
       </c>
-      <c r="H607" s="6" t="inlineStr"/>
-      <c r="I607" s="6" t="inlineStr"/>
-      <c r="J607" s="6" t="inlineStr"/>
-      <c r="K607" s="6" t="inlineStr"/>
+      <c r="H607" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I607" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J607" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K607" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="608">
       <c r="A608" s="2" t="inlineStr">
@@ -27223,10 +28213,20 @@
       <c r="G608" s="2" t="n">
         <v>3.55</v>
       </c>
-      <c r="H608" s="6" t="inlineStr"/>
-      <c r="I608" s="6" t="inlineStr"/>
-      <c r="J608" s="6" t="inlineStr"/>
-      <c r="K608" s="6" t="inlineStr"/>
+      <c r="H608" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I608" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J608" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K608" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="609">
       <c r="A609" s="2" t="inlineStr">
@@ -27262,10 +28262,20 @@
       <c r="G609" s="2" t="n">
         <v>2.24</v>
       </c>
-      <c r="H609" s="6" t="inlineStr"/>
-      <c r="I609" s="6" t="inlineStr"/>
-      <c r="J609" s="6" t="inlineStr"/>
-      <c r="K609" s="6" t="inlineStr"/>
+      <c r="H609" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I609" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J609" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K609" s="4" t="n">
+        <v>124</v>
+      </c>
     </row>
     <row r="610">
       <c r="A610" s="2" t="inlineStr">
@@ -27613,10 +28623,20 @@
       <c r="G618" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="H618" s="6" t="inlineStr"/>
-      <c r="I618" s="6" t="inlineStr"/>
-      <c r="J618" s="6" t="inlineStr"/>
-      <c r="K618" s="6" t="inlineStr"/>
+      <c r="H618" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I618" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J618" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K618" s="5" t="n">
+        <v>-1000</v>
+      </c>
     </row>
     <row r="619">
       <c r="A619" s="2" t="inlineStr">
@@ -27652,10 +28672,20 @@
       <c r="G619" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="H619" s="6" t="inlineStr"/>
-      <c r="I619" s="6" t="inlineStr"/>
-      <c r="J619" s="6" t="inlineStr"/>
-      <c r="K619" s="6" t="inlineStr"/>
+      <c r="H619" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I619" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J619" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K619" s="5" t="n">
+        <v>-250</v>
+      </c>
     </row>
     <row r="620">
       <c r="A620" s="2" t="inlineStr">
@@ -27691,10 +28721,20 @@
       <c r="G620" s="2" t="n">
         <v>2.34</v>
       </c>
-      <c r="H620" s="6" t="inlineStr"/>
-      <c r="I620" s="6" t="inlineStr"/>
-      <c r="J620" s="6" t="inlineStr"/>
-      <c r="K620" s="6" t="inlineStr"/>
+      <c r="H620" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I620" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J620" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K620" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="621">
       <c r="A621" s="2" t="inlineStr">
@@ -27847,10 +28887,20 @@
       <c r="G624" s="2" t="n">
         <v>3.85</v>
       </c>
-      <c r="H624" s="6" t="inlineStr"/>
-      <c r="I624" s="6" t="inlineStr"/>
-      <c r="J624" s="6" t="inlineStr"/>
-      <c r="K624" s="6" t="inlineStr"/>
+      <c r="H624" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I624" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J624" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K624" s="5" t="n">
+        <v>-285</v>
+      </c>
     </row>
     <row r="625">
       <c r="A625" s="2" t="inlineStr">
@@ -27886,10 +28936,20 @@
       <c r="G625" s="2" t="n">
         <v>1.9</v>
       </c>
-      <c r="H625" s="6" t="inlineStr"/>
-      <c r="I625" s="6" t="inlineStr"/>
-      <c r="J625" s="6" t="inlineStr"/>
-      <c r="K625" s="6" t="inlineStr"/>
+      <c r="H625" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I625" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J625" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K625" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="626">
       <c r="A626" s="2" t="inlineStr">
@@ -28003,10 +29063,20 @@
       <c r="G628" s="2" t="n">
         <v>3.45</v>
       </c>
-      <c r="H628" s="6" t="inlineStr"/>
-      <c r="I628" s="6" t="inlineStr"/>
-      <c r="J628" s="6" t="inlineStr"/>
-      <c r="K628" s="6" t="inlineStr"/>
+      <c r="H628" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I628" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J628" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K628" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="629">
       <c r="A629" s="2" t="inlineStr">
@@ -28042,10 +29112,20 @@
       <c r="G629" s="2" t="n">
         <v>2.02</v>
       </c>
-      <c r="H629" s="6" t="inlineStr"/>
-      <c r="I629" s="6" t="inlineStr"/>
-      <c r="J629" s="6" t="inlineStr"/>
-      <c r="K629" s="6" t="inlineStr"/>
+      <c r="H629" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I629" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J629" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K629" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="630">
       <c r="A630" s="2" t="inlineStr">
@@ -28081,10 +29161,20 @@
       <c r="G630" s="2" t="n">
         <v>3.65</v>
       </c>
-      <c r="H630" s="6" t="inlineStr"/>
-      <c r="I630" s="6" t="inlineStr"/>
-      <c r="J630" s="6" t="inlineStr"/>
-      <c r="K630" s="6" t="inlineStr"/>
+      <c r="H630" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I630" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J630" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K630" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="631">
       <c r="A631" s="2" t="inlineStr">
@@ -28120,10 +29210,20 @@
       <c r="G631" s="2" t="n">
         <v>2.12</v>
       </c>
-      <c r="H631" s="6" t="inlineStr"/>
-      <c r="I631" s="6" t="inlineStr"/>
-      <c r="J631" s="6" t="inlineStr"/>
-      <c r="K631" s="6" t="inlineStr"/>
+      <c r="H631" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I631" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J631" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K631" s="4" t="n">
+        <v>112</v>
+      </c>
     </row>
     <row r="632">
       <c r="A632" s="2" t="inlineStr">
@@ -28159,10 +29259,20 @@
       <c r="G632" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="H632" s="6" t="inlineStr"/>
-      <c r="I632" s="6" t="inlineStr"/>
-      <c r="J632" s="6" t="inlineStr"/>
-      <c r="K632" s="6" t="inlineStr"/>
+      <c r="H632" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I632" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J632" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K632" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="633">
       <c r="A633" s="2" t="inlineStr">
@@ -28198,10 +29308,20 @@
       <c r="G633" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="H633" s="6" t="inlineStr"/>
-      <c r="I633" s="6" t="inlineStr"/>
-      <c r="J633" s="6" t="inlineStr"/>
-      <c r="K633" s="6" t="inlineStr"/>
+      <c r="H633" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I633" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J633" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K633" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="634">
       <c r="A634" s="2" t="inlineStr">
@@ -28237,10 +29357,20 @@
       <c r="G634" s="2" t="n">
         <v>2.16</v>
       </c>
-      <c r="H634" s="6" t="inlineStr"/>
-      <c r="I634" s="6" t="inlineStr"/>
-      <c r="J634" s="6" t="inlineStr"/>
-      <c r="K634" s="6" t="inlineStr"/>
+      <c r="H634" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I634" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J634" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K634" s="4" t="n">
+        <v>116</v>
+      </c>
     </row>
     <row r="635">
       <c r="A635" s="2" t="inlineStr">
@@ -28354,10 +29484,20 @@
       <c r="G637" s="2" t="n">
         <v>3.95</v>
       </c>
-      <c r="H637" s="6" t="inlineStr"/>
-      <c r="I637" s="6" t="inlineStr"/>
-      <c r="J637" s="6" t="inlineStr"/>
-      <c r="K637" s="6" t="inlineStr"/>
+      <c r="H637" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I637" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J637" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K637" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="638">
       <c r="A638" s="2" t="inlineStr">
@@ -28510,10 +29650,20 @@
       <c r="G641" s="2" t="n">
         <v>3.7</v>
       </c>
-      <c r="H641" s="6" t="inlineStr"/>
-      <c r="I641" s="6" t="inlineStr"/>
-      <c r="J641" s="6" t="inlineStr"/>
-      <c r="K641" s="6" t="inlineStr"/>
+      <c r="H641" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I641" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J641" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K641" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="642">
       <c r="A642" s="2" t="inlineStr">
@@ -28549,10 +29699,20 @@
       <c r="G642" s="2" t="n">
         <v>1.83</v>
       </c>
-      <c r="H642" s="6" t="inlineStr"/>
-      <c r="I642" s="6" t="inlineStr"/>
-      <c r="J642" s="6" t="inlineStr"/>
-      <c r="K642" s="6" t="inlineStr"/>
+      <c r="H642" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I642" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J642" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K642" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="643">
       <c r="A643" s="2" t="inlineStr">
@@ -28588,10 +29748,20 @@
       <c r="G643" s="2" t="n">
         <v>4.4</v>
       </c>
-      <c r="H643" s="6" t="inlineStr"/>
-      <c r="I643" s="6" t="inlineStr"/>
-      <c r="J643" s="6" t="inlineStr"/>
-      <c r="K643" s="6" t="inlineStr"/>
+      <c r="H643" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I643" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J643" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K643" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="644">
       <c r="A644" s="2" t="inlineStr">
@@ -28627,10 +29797,20 @@
       <c r="G644" s="2" t="n">
         <v>10.5</v>
       </c>
-      <c r="H644" s="6" t="inlineStr"/>
-      <c r="I644" s="6" t="inlineStr"/>
-      <c r="J644" s="6" t="inlineStr"/>
-      <c r="K644" s="6" t="inlineStr"/>
+      <c r="H644" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I644" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J644" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K644" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="645">
       <c r="A645" s="2" t="inlineStr">
@@ -28666,10 +29846,20 @@
       <c r="G645" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="H645" s="6" t="inlineStr"/>
-      <c r="I645" s="6" t="inlineStr"/>
-      <c r="J645" s="6" t="inlineStr"/>
-      <c r="K645" s="6" t="inlineStr"/>
+      <c r="H645" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I645" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J645" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K645" s="5" t="n">
+        <v>-250</v>
+      </c>
     </row>
     <row r="646">
       <c r="A646" s="2" t="inlineStr">
@@ -28705,10 +29895,20 @@
       <c r="G646" s="2" t="n">
         <v>2.3</v>
       </c>
-      <c r="H646" s="6" t="inlineStr"/>
-      <c r="I646" s="6" t="inlineStr"/>
-      <c r="J646" s="6" t="inlineStr"/>
-      <c r="K646" s="6" t="inlineStr"/>
+      <c r="H646" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I646" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J646" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K646" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="647">
       <c r="A647" s="2" t="inlineStr">
@@ -28744,10 +29944,20 @@
       <c r="G647" s="2" t="n">
         <v>2.2</v>
       </c>
-      <c r="H647" s="6" t="inlineStr"/>
-      <c r="I647" s="6" t="inlineStr"/>
-      <c r="J647" s="6" t="inlineStr"/>
-      <c r="K647" s="6" t="inlineStr"/>
+      <c r="H647" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I647" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J647" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K647" s="5" t="n">
+        <v>-120</v>
+      </c>
     </row>
     <row r="648">
       <c r="A648" s="2" t="inlineStr">
@@ -28783,10 +29993,20 @@
       <c r="G648" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="H648" s="6" t="inlineStr"/>
-      <c r="I648" s="6" t="inlineStr"/>
-      <c r="J648" s="6" t="inlineStr"/>
-      <c r="K648" s="6" t="inlineStr"/>
+      <c r="H648" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I648" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J648" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K648" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="649">
       <c r="A649" s="2" t="inlineStr">
@@ -28822,10 +30042,20 @@
       <c r="G649" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="H649" s="6" t="inlineStr"/>
-      <c r="I649" s="6" t="inlineStr"/>
-      <c r="J649" s="6" t="inlineStr"/>
-      <c r="K649" s="6" t="inlineStr"/>
+      <c r="H649" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I649" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J649" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K649" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="650">
       <c r="A650" s="2" t="inlineStr">
@@ -28861,10 +30091,20 @@
       <c r="G650" s="2" t="n">
         <v>3.45</v>
       </c>
-      <c r="H650" s="6" t="inlineStr"/>
-      <c r="I650" s="6" t="inlineStr"/>
-      <c r="J650" s="6" t="inlineStr"/>
-      <c r="K650" s="6" t="inlineStr"/>
+      <c r="H650" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I650" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J650" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K650" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="651">
       <c r="A651" s="2" t="inlineStr">
@@ -28900,10 +30140,20 @@
       <c r="G651" s="2" t="n">
         <v>2.16</v>
       </c>
-      <c r="H651" s="6" t="inlineStr"/>
-      <c r="I651" s="6" t="inlineStr"/>
-      <c r="J651" s="6" t="inlineStr"/>
-      <c r="K651" s="6" t="inlineStr"/>
+      <c r="H651" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I651" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J651" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K651" s="4" t="n">
+        <v>116</v>
+      </c>
     </row>
     <row r="652">
       <c r="A652" s="2" t="inlineStr">
@@ -28978,10 +30228,20 @@
       <c r="G653" s="2" t="n">
         <v>4.5</v>
       </c>
-      <c r="H653" s="6" t="inlineStr"/>
-      <c r="I653" s="6" t="inlineStr"/>
-      <c r="J653" s="6" t="inlineStr"/>
-      <c r="K653" s="6" t="inlineStr"/>
+      <c r="H653" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I653" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J653" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K653" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="654">
       <c r="A654" s="2" t="inlineStr">
@@ -29017,10 +30277,20 @@
       <c r="G654" s="2" t="n">
         <v>3.95</v>
       </c>
-      <c r="H654" s="6" t="inlineStr"/>
-      <c r="I654" s="6" t="inlineStr"/>
-      <c r="J654" s="6" t="inlineStr"/>
-      <c r="K654" s="6" t="inlineStr"/>
+      <c r="H654" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I654" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J654" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K654" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="655">
       <c r="A655" s="2" t="inlineStr">
@@ -29056,10 +30326,20 @@
       <c r="G655" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H655" s="6" t="inlineStr"/>
-      <c r="I655" s="6" t="inlineStr"/>
-      <c r="J655" s="6" t="inlineStr"/>
-      <c r="K655" s="6" t="inlineStr"/>
+      <c r="H655" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I655" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J655" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K655" s="4" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="656">
       <c r="A656" s="2" t="inlineStr">
@@ -29095,10 +30375,20 @@
       <c r="G656" s="2" t="n">
         <v>4.5</v>
       </c>
-      <c r="H656" s="6" t="inlineStr"/>
-      <c r="I656" s="6" t="inlineStr"/>
-      <c r="J656" s="6" t="inlineStr"/>
-      <c r="K656" s="6" t="inlineStr"/>
+      <c r="H656" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I656" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J656" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K656" s="5" t="n">
+        <v>-350</v>
+      </c>
     </row>
     <row r="657">
       <c r="A657" s="2" t="inlineStr">
@@ -29134,10 +30424,20 @@
       <c r="G657" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="H657" s="6" t="inlineStr"/>
-      <c r="I657" s="6" t="inlineStr"/>
-      <c r="J657" s="6" t="inlineStr"/>
-      <c r="K657" s="6" t="inlineStr"/>
+      <c r="H657" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I657" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J657" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K657" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="658">
       <c r="A658" s="2" t="inlineStr">
@@ -29212,10 +30512,20 @@
       <c r="G659" s="2" t="n">
         <v>3.65</v>
       </c>
-      <c r="H659" s="6" t="inlineStr"/>
-      <c r="I659" s="6" t="inlineStr"/>
-      <c r="J659" s="6" t="inlineStr"/>
-      <c r="K659" s="6" t="inlineStr"/>
+      <c r="H659" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I659" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J659" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K659" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="660">
       <c r="A660" s="2" t="inlineStr">
@@ -29251,10 +30561,20 @@
       <c r="G660" s="2" t="n">
         <v>1.81</v>
       </c>
-      <c r="H660" s="6" t="inlineStr"/>
-      <c r="I660" s="6" t="inlineStr"/>
-      <c r="J660" s="6" t="inlineStr"/>
-      <c r="K660" s="6" t="inlineStr"/>
+      <c r="H660" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I660" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J660" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K660" s="4" t="n">
+        <v>81</v>
+      </c>
     </row>
     <row r="661">
       <c r="A661" s="2" t="inlineStr">
@@ -29290,10 +30610,20 @@
       <c r="G661" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="H661" s="6" t="inlineStr"/>
-      <c r="I661" s="6" t="inlineStr"/>
-      <c r="J661" s="6" t="inlineStr"/>
-      <c r="K661" s="6" t="inlineStr"/>
+      <c r="H661" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I661" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J661" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K661" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="662">
       <c r="A662" s="2" t="inlineStr">
@@ -29329,10 +30659,20 @@
       <c r="G662" s="2" t="n">
         <v>1.92</v>
       </c>
-      <c r="H662" s="6" t="inlineStr"/>
-      <c r="I662" s="6" t="inlineStr"/>
-      <c r="J662" s="6" t="inlineStr"/>
-      <c r="K662" s="6" t="inlineStr"/>
+      <c r="H662" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I662" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J662" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K662" s="4" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="663">
       <c r="A663" s="2" t="inlineStr">
@@ -29368,10 +30708,20 @@
       <c r="G663" s="2" t="n">
         <v>3.6</v>
       </c>
-      <c r="H663" s="6" t="inlineStr"/>
-      <c r="I663" s="6" t="inlineStr"/>
-      <c r="J663" s="6" t="inlineStr"/>
-      <c r="K663" s="6" t="inlineStr"/>
+      <c r="H663" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I663" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J663" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K663" s="5" t="n">
+        <v>-260</v>
+      </c>
     </row>
     <row r="664">
       <c r="A664" s="2" t="inlineStr">
@@ -29407,10 +30757,20 @@
       <c r="G664" s="2" t="n">
         <v>1.96</v>
       </c>
-      <c r="H664" s="6" t="inlineStr"/>
-      <c r="I664" s="6" t="inlineStr"/>
-      <c r="J664" s="6" t="inlineStr"/>
-      <c r="K664" s="6" t="inlineStr"/>
+      <c r="H664" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I664" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J664" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K664" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="665">
       <c r="A665" s="2" t="inlineStr">
@@ -29446,10 +30806,20 @@
       <c r="G665" s="2" t="n">
         <v>3.7</v>
       </c>
-      <c r="H665" s="6" t="inlineStr"/>
-      <c r="I665" s="6" t="inlineStr"/>
-      <c r="J665" s="6" t="inlineStr"/>
-      <c r="K665" s="6" t="inlineStr"/>
+      <c r="H665" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I665" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J665" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K665" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="666">
       <c r="A666" s="2" t="inlineStr">
@@ -29485,10 +30855,20 @@
       <c r="G666" s="2" t="n">
         <v>1.98</v>
       </c>
-      <c r="H666" s="6" t="inlineStr"/>
-      <c r="I666" s="6" t="inlineStr"/>
-      <c r="J666" s="6" t="inlineStr"/>
-      <c r="K666" s="6" t="inlineStr"/>
+      <c r="H666" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I666" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J666" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K666" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="667">
       <c r="A667" s="2" t="inlineStr">
@@ -29524,10 +30904,20 @@
       <c r="G667" s="2" t="n">
         <v>3.85</v>
       </c>
-      <c r="H667" s="6" t="inlineStr"/>
-      <c r="I667" s="6" t="inlineStr"/>
-      <c r="J667" s="6" t="inlineStr"/>
-      <c r="K667" s="6" t="inlineStr"/>
+      <c r="H667" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I667" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J667" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K667" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="668">
       <c r="A668" s="2" t="inlineStr">
@@ -29563,10 +30953,20 @@
       <c r="G668" s="2" t="n">
         <v>4.2</v>
       </c>
-      <c r="H668" s="6" t="inlineStr"/>
-      <c r="I668" s="6" t="inlineStr"/>
-      <c r="J668" s="6" t="inlineStr"/>
-      <c r="K668" s="6" t="inlineStr"/>
+      <c r="H668" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I668" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J668" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K668" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="669">
       <c r="A669" s="2" t="inlineStr">
@@ -29641,10 +31041,20 @@
       <c r="G670" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="H670" s="6" t="inlineStr"/>
-      <c r="I670" s="6" t="inlineStr"/>
-      <c r="J670" s="6" t="inlineStr"/>
-      <c r="K670" s="6" t="inlineStr"/>
+      <c r="H670" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I670" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J670" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K670" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="671">
       <c r="A671" s="2" t="inlineStr">
@@ -29680,10 +31090,20 @@
       <c r="G671" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="H671" s="6" t="inlineStr"/>
-      <c r="I671" s="6" t="inlineStr"/>
-      <c r="J671" s="6" t="inlineStr"/>
-      <c r="K671" s="6" t="inlineStr"/>
+      <c r="H671" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I671" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J671" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K671" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="672">
       <c r="A672" s="2" t="inlineStr">
@@ -29719,10 +31139,20 @@
       <c r="G672" s="2" t="n">
         <v>2.2</v>
       </c>
-      <c r="H672" s="6" t="inlineStr"/>
-      <c r="I672" s="6" t="inlineStr"/>
-      <c r="J672" s="6" t="inlineStr"/>
-      <c r="K672" s="6" t="inlineStr"/>
+      <c r="H672" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I672" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J672" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K672" s="4" t="n">
+        <v>120</v>
+      </c>
     </row>
     <row r="673">
       <c r="A673" s="2" t="inlineStr">
@@ -29797,10 +31227,20 @@
       <c r="G674" s="2" t="n">
         <v>4.3</v>
       </c>
-      <c r="H674" s="6" t="inlineStr"/>
-      <c r="I674" s="6" t="inlineStr"/>
-      <c r="J674" s="6" t="inlineStr"/>
-      <c r="K674" s="6" t="inlineStr"/>
+      <c r="H674" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I674" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J674" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K674" s="5" t="n">
+        <v>-330</v>
+      </c>
     </row>
     <row r="675">
       <c r="A675" s="2" t="inlineStr">
@@ -29836,10 +31276,20 @@
       <c r="G675" s="2" t="n">
         <v>1.8</v>
       </c>
-      <c r="H675" s="6" t="inlineStr"/>
-      <c r="I675" s="6" t="inlineStr"/>
-      <c r="J675" s="6" t="inlineStr"/>
-      <c r="K675" s="6" t="inlineStr"/>
+      <c r="H675" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I675" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J675" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K675" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="676">
       <c r="A676" s="2" t="inlineStr">
@@ -29875,10 +31325,20 @@
       <c r="G676" s="2" t="n">
         <v>3.8</v>
       </c>
-      <c r="H676" s="6" t="inlineStr"/>
-      <c r="I676" s="6" t="inlineStr"/>
-      <c r="J676" s="6" t="inlineStr"/>
-      <c r="K676" s="6" t="inlineStr"/>
+      <c r="H676" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I676" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J676" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K676" s="5" t="n">
+        <v>-280</v>
+      </c>
     </row>
     <row r="677">
       <c r="A677" s="2" t="inlineStr">
@@ -29914,10 +31374,20 @@
       <c r="G677" s="2" t="n">
         <v>1.84</v>
       </c>
-      <c r="H677" s="6" t="inlineStr"/>
-      <c r="I677" s="6" t="inlineStr"/>
-      <c r="J677" s="6" t="inlineStr"/>
-      <c r="K677" s="6" t="inlineStr"/>
+      <c r="H677" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I677" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J677" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K677" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="678">
       <c r="A678" s="2" t="inlineStr">
@@ -29953,10 +31423,20 @@
       <c r="G678" s="2" t="n">
         <v>4.5</v>
       </c>
-      <c r="H678" s="6" t="inlineStr"/>
-      <c r="I678" s="6" t="inlineStr"/>
-      <c r="J678" s="6" t="inlineStr"/>
-      <c r="K678" s="6" t="inlineStr"/>
+      <c r="H678" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I678" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J678" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K678" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="679">
       <c r="A679" s="2" t="inlineStr">
@@ -29992,10 +31472,20 @@
       <c r="G679" s="2" t="n">
         <v>1.9</v>
       </c>
-      <c r="H679" s="6" t="inlineStr"/>
-      <c r="I679" s="6" t="inlineStr"/>
-      <c r="J679" s="6" t="inlineStr"/>
-      <c r="K679" s="6" t="inlineStr"/>
+      <c r="H679" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I679" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J679" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K679" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="680">
       <c r="A680" s="2" t="inlineStr">
@@ -30031,10 +31521,20 @@
       <c r="G680" s="2" t="n">
         <v>3.85</v>
       </c>
-      <c r="H680" s="6" t="inlineStr"/>
-      <c r="I680" s="6" t="inlineStr"/>
-      <c r="J680" s="6" t="inlineStr"/>
-      <c r="K680" s="6" t="inlineStr"/>
+      <c r="H680" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I680" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J680" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K680" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="681">
       <c r="A681" s="2" t="inlineStr">
@@ -30070,10 +31570,20 @@
       <c r="G681" s="2" t="n">
         <v>3.7</v>
       </c>
-      <c r="H681" s="6" t="inlineStr"/>
-      <c r="I681" s="6" t="inlineStr"/>
-      <c r="J681" s="6" t="inlineStr"/>
-      <c r="K681" s="6" t="inlineStr"/>
+      <c r="H681" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I681" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J681" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K681" s="5" t="n">
+        <v>-270</v>
+      </c>
     </row>
     <row r="682">
       <c r="A682" s="2" t="inlineStr">
@@ -30109,10 +31619,20 @@
       <c r="G682" s="2" t="n">
         <v>1.88</v>
       </c>
-      <c r="H682" s="6" t="inlineStr"/>
-      <c r="I682" s="6" t="inlineStr"/>
-      <c r="J682" s="6" t="inlineStr"/>
-      <c r="K682" s="6" t="inlineStr"/>
+      <c r="H682" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I682" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J682" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K682" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="683">
       <c r="A683" s="2" t="inlineStr">
@@ -30148,10 +31668,20 @@
       <c r="G683" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="H683" s="6" t="inlineStr"/>
-      <c r="I683" s="6" t="inlineStr"/>
-      <c r="J683" s="6" t="inlineStr"/>
-      <c r="K683" s="6" t="inlineStr"/>
+      <c r="H683" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I683" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J683" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K683" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="684">
       <c r="A684" s="2" t="inlineStr">
@@ -30187,10 +31717,20 @@
       <c r="G684" s="2" t="n">
         <v>3.6</v>
       </c>
-      <c r="H684" s="6" t="inlineStr"/>
-      <c r="I684" s="6" t="inlineStr"/>
-      <c r="J684" s="6" t="inlineStr"/>
-      <c r="K684" s="6" t="inlineStr"/>
+      <c r="H684" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I684" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J684" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K684" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="685">
       <c r="A685" s="2" t="inlineStr">
@@ -30226,10 +31766,20 @@
       <c r="G685" s="2" t="n">
         <v>2.22</v>
       </c>
-      <c r="H685" s="6" t="inlineStr"/>
-      <c r="I685" s="6" t="inlineStr"/>
-      <c r="J685" s="6" t="inlineStr"/>
-      <c r="K685" s="6" t="inlineStr"/>
+      <c r="H685" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I685" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J685" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K685" s="4" t="n">
+        <v>122</v>
+      </c>
     </row>
     <row r="686">
       <c r="A686" s="2" t="inlineStr">
@@ -30265,10 +31815,20 @@
       <c r="G686" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="H686" s="6" t="inlineStr"/>
-      <c r="I686" s="6" t="inlineStr"/>
-      <c r="J686" s="6" t="inlineStr"/>
-      <c r="K686" s="6" t="inlineStr"/>
+      <c r="H686" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I686" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J686" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K686" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="687">
       <c r="A687" s="2" t="inlineStr">
@@ -30304,10 +31864,20 @@
       <c r="G687" s="2" t="n">
         <v>3.95</v>
       </c>
-      <c r="H687" s="6" t="inlineStr"/>
-      <c r="I687" s="6" t="inlineStr"/>
-      <c r="J687" s="6" t="inlineStr"/>
-      <c r="K687" s="6" t="inlineStr"/>
+      <c r="H687" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I687" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J687" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K687" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="688">
       <c r="A688" s="2" t="inlineStr">
@@ -30343,10 +31913,20 @@
       <c r="G688" s="2" t="n">
         <v>1.87</v>
       </c>
-      <c r="H688" s="6" t="inlineStr"/>
-      <c r="I688" s="6" t="inlineStr"/>
-      <c r="J688" s="6" t="inlineStr"/>
-      <c r="K688" s="6" t="inlineStr"/>
+      <c r="H688" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I688" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J688" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K688" s="4" t="n">
+        <v>87</v>
+      </c>
     </row>
     <row r="689">
       <c r="A689" s="2" t="inlineStr">
@@ -30382,10 +31962,20 @@
       <c r="G689" s="2" t="n">
         <v>4.1</v>
       </c>
-      <c r="H689" s="6" t="inlineStr"/>
-      <c r="I689" s="6" t="inlineStr"/>
-      <c r="J689" s="6" t="inlineStr"/>
-      <c r="K689" s="6" t="inlineStr"/>
+      <c r="H689" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I689" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J689" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K689" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="690">
       <c r="A690" s="2" t="inlineStr">
@@ -30421,10 +32011,20 @@
       <c r="G690" s="2" t="n">
         <v>1.81</v>
       </c>
-      <c r="H690" s="6" t="inlineStr"/>
-      <c r="I690" s="6" t="inlineStr"/>
-      <c r="J690" s="6" t="inlineStr"/>
-      <c r="K690" s="6" t="inlineStr"/>
+      <c r="H690" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I690" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J690" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K690" s="4" t="n">
+        <v>81</v>
+      </c>
     </row>
     <row r="691">
       <c r="A691" s="2" t="inlineStr">
@@ -30460,10 +32060,20 @@
       <c r="G691" s="2" t="n">
         <v>3.6</v>
       </c>
-      <c r="H691" s="6" t="inlineStr"/>
-      <c r="I691" s="6" t="inlineStr"/>
-      <c r="J691" s="6" t="inlineStr"/>
-      <c r="K691" s="6" t="inlineStr"/>
+      <c r="H691" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I691" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J691" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K691" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="692">
       <c r="A692" s="2" t="inlineStr">
@@ -30499,10 +32109,20 @@
       <c r="G692" s="2" t="n">
         <v>1.94</v>
       </c>
-      <c r="H692" s="6" t="inlineStr"/>
-      <c r="I692" s="6" t="inlineStr"/>
-      <c r="J692" s="6" t="inlineStr"/>
-      <c r="K692" s="6" t="inlineStr"/>
+      <c r="H692" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I692" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J692" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K692" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="693">
       <c r="A693" s="2" t="inlineStr">
@@ -30538,10 +32158,20 @@
       <c r="G693" s="2" t="n">
         <v>4.3</v>
       </c>
-      <c r="H693" s="6" t="inlineStr"/>
-      <c r="I693" s="6" t="inlineStr"/>
-      <c r="J693" s="6" t="inlineStr"/>
-      <c r="K693" s="6" t="inlineStr"/>
+      <c r="H693" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I693" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J693" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K693" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="694">
       <c r="A694" s="2" t="inlineStr">
@@ -30577,10 +32207,20 @@
       <c r="G694" s="2" t="n">
         <v>1.91</v>
       </c>
-      <c r="H694" s="6" t="inlineStr"/>
-      <c r="I694" s="6" t="inlineStr"/>
-      <c r="J694" s="6" t="inlineStr"/>
-      <c r="K694" s="6" t="inlineStr"/>
+      <c r="H694" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I694" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J694" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K694" s="4" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="695">
       <c r="A695" s="2" t="inlineStr">
@@ -30616,10 +32256,20 @@
       <c r="G695" s="2" t="n">
         <v>3.7</v>
       </c>
-      <c r="H695" s="6" t="inlineStr"/>
-      <c r="I695" s="6" t="inlineStr"/>
-      <c r="J695" s="6" t="inlineStr"/>
-      <c r="K695" s="6" t="inlineStr"/>
+      <c r="H695" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I695" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J695" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K695" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="696">
       <c r="A696" s="2" t="inlineStr">
@@ -30655,10 +32305,20 @@
       <c r="G696" s="2" t="n">
         <v>1.86</v>
       </c>
-      <c r="H696" s="6" t="inlineStr"/>
-      <c r="I696" s="6" t="inlineStr"/>
-      <c r="J696" s="6" t="inlineStr"/>
-      <c r="K696" s="6" t="inlineStr"/>
+      <c r="H696" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I696" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J696" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K696" s="4" t="n">
+        <v>86</v>
+      </c>
     </row>
     <row r="697">
       <c r="A697" s="2" t="inlineStr">
@@ -30694,10 +32354,20 @@
       <c r="G697" s="2" t="n">
         <v>3.75</v>
       </c>
-      <c r="H697" s="6" t="inlineStr"/>
-      <c r="I697" s="6" t="inlineStr"/>
-      <c r="J697" s="6" t="inlineStr"/>
-      <c r="K697" s="6" t="inlineStr"/>
+      <c r="H697" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I697" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J697" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K697" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="698">
       <c r="A698" s="2" t="inlineStr">
@@ -30733,10 +32403,20 @@
       <c r="G698" s="2" t="n">
         <v>1.93</v>
       </c>
-      <c r="H698" s="6" t="inlineStr"/>
-      <c r="I698" s="6" t="inlineStr"/>
-      <c r="J698" s="6" t="inlineStr"/>
-      <c r="K698" s="6" t="inlineStr"/>
+      <c r="H698" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I698" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J698" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K698" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="699">
       <c r="A699" s="2" t="inlineStr">
@@ -30772,10 +32452,20 @@
       <c r="G699" s="2" t="n">
         <v>3.9</v>
       </c>
-      <c r="H699" s="6" t="inlineStr"/>
-      <c r="I699" s="6" t="inlineStr"/>
-      <c r="J699" s="6" t="inlineStr"/>
-      <c r="K699" s="6" t="inlineStr"/>
+      <c r="H699" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I699" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J699" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K699" s="5" t="n">
+        <v>-290</v>
+      </c>
     </row>
     <row r="700">
       <c r="A700" s="2" t="inlineStr">
@@ -30811,10 +32501,20 @@
       <c r="G700" s="2" t="n">
         <v>1.9</v>
       </c>
-      <c r="H700" s="6" t="inlineStr"/>
-      <c r="I700" s="6" t="inlineStr"/>
-      <c r="J700" s="6" t="inlineStr"/>
-      <c r="K700" s="6" t="inlineStr"/>
+      <c r="H700" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I700" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J700" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K700" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="701">
       <c r="A701" s="2" t="inlineStr">
@@ -30850,10 +32550,20 @@
       <c r="G701" s="2" t="n">
         <v>3.95</v>
       </c>
-      <c r="H701" s="6" t="inlineStr"/>
-      <c r="I701" s="6" t="inlineStr"/>
-      <c r="J701" s="6" t="inlineStr"/>
-      <c r="K701" s="6" t="inlineStr"/>
+      <c r="H701" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I701" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J701" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K701" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="702">
       <c r="A702" s="2" t="inlineStr">
@@ -30889,10 +32599,20 @@
       <c r="G702" s="2" t="n">
         <v>4.4</v>
       </c>
-      <c r="H702" s="6" t="inlineStr"/>
-      <c r="I702" s="6" t="inlineStr"/>
-      <c r="J702" s="6" t="inlineStr"/>
-      <c r="K702" s="6" t="inlineStr"/>
+      <c r="H702" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I702" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J702" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K702" s="5" t="n">
+        <v>-340</v>
+      </c>
     </row>
     <row r="703">
       <c r="A703" s="2" t="inlineStr">
@@ -30928,10 +32648,20 @@
       <c r="G703" s="2" t="n">
         <v>3.65</v>
       </c>
-      <c r="H703" s="6" t="inlineStr"/>
-      <c r="I703" s="6" t="inlineStr"/>
-      <c r="J703" s="6" t="inlineStr"/>
-      <c r="K703" s="6" t="inlineStr"/>
+      <c r="H703" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I703" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J703" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K703" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="704">
       <c r="A704" s="2" t="inlineStr">
@@ -30967,10 +32697,20 @@
       <c r="G704" s="2" t="n">
         <v>1.92</v>
       </c>
-      <c r="H704" s="6" t="inlineStr"/>
-      <c r="I704" s="6" t="inlineStr"/>
-      <c r="J704" s="6" t="inlineStr"/>
-      <c r="K704" s="6" t="inlineStr"/>
+      <c r="H704" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I704" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J704" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K704" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="705">
       <c r="A705" s="2" t="inlineStr">
@@ -31006,10 +32746,20 @@
       <c r="G705" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="H705" s="6" t="inlineStr"/>
-      <c r="I705" s="6" t="inlineStr"/>
-      <c r="J705" s="6" t="inlineStr"/>
-      <c r="K705" s="6" t="inlineStr"/>
+      <c r="H705" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I705" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J705" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K705" s="5" t="n">
+        <v>-300</v>
+      </c>
     </row>
     <row r="706">
       <c r="A706" s="2" t="inlineStr">
@@ -31045,10 +32795,20 @@
       <c r="G706" s="2" t="n">
         <v>4.3</v>
       </c>
-      <c r="H706" s="6" t="inlineStr"/>
-      <c r="I706" s="6" t="inlineStr"/>
-      <c r="J706" s="6" t="inlineStr"/>
-      <c r="K706" s="6" t="inlineStr"/>
+      <c r="H706" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I706" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J706" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K706" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="707">
       <c r="A707" s="2" t="inlineStr">
@@ -31084,10 +32844,20 @@
       <c r="G707" s="2" t="n">
         <v>4.2</v>
       </c>
-      <c r="H707" s="6" t="inlineStr"/>
-      <c r="I707" s="6" t="inlineStr"/>
-      <c r="J707" s="6" t="inlineStr"/>
-      <c r="K707" s="6" t="inlineStr"/>
+      <c r="H707" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I707" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J707" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K707" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="708">
       <c r="A708" s="2" t="inlineStr">
@@ -31123,10 +32893,20 @@
       <c r="G708" s="2" t="n">
         <v>4.1</v>
       </c>
-      <c r="H708" s="6" t="inlineStr"/>
-      <c r="I708" s="6" t="inlineStr"/>
-      <c r="J708" s="6" t="inlineStr"/>
-      <c r="K708" s="6" t="inlineStr"/>
+      <c r="H708" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I708" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J708" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K708" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="709">
       <c r="A709" s="2" t="inlineStr">
@@ -31162,10 +32942,20 @@
       <c r="G709" s="2" t="n">
         <v>4.5</v>
       </c>
-      <c r="H709" s="6" t="inlineStr"/>
-      <c r="I709" s="6" t="inlineStr"/>
-      <c r="J709" s="6" t="inlineStr"/>
-      <c r="K709" s="6" t="inlineStr"/>
+      <c r="H709" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I709" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J709" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K709" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="710">
       <c r="A710" s="2" t="inlineStr">
@@ -31201,10 +32991,20 @@
       <c r="G710" s="2" t="n">
         <v>4.3</v>
       </c>
-      <c r="H710" s="6" t="inlineStr"/>
-      <c r="I710" s="6" t="inlineStr"/>
-      <c r="J710" s="6" t="inlineStr"/>
-      <c r="K710" s="6" t="inlineStr"/>
+      <c r="H710" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I710" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J710" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K710" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="711">
       <c r="A711" s="2" t="inlineStr">
@@ -31240,10 +33040,20 @@
       <c r="G711" s="2" t="n">
         <v>1.88</v>
       </c>
-      <c r="H711" s="6" t="inlineStr"/>
-      <c r="I711" s="6" t="inlineStr"/>
-      <c r="J711" s="6" t="inlineStr"/>
-      <c r="K711" s="6" t="inlineStr"/>
+      <c r="H711" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I711" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J711" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K711" s="4" t="n">
+        <v>88</v>
+      </c>
     </row>
     <row r="712">
       <c r="A712" s="2" t="inlineStr">
@@ -31279,10 +33089,20 @@
       <c r="G712" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="H712" s="6" t="inlineStr"/>
-      <c r="I712" s="6" t="inlineStr"/>
-      <c r="J712" s="6" t="inlineStr"/>
-      <c r="K712" s="6" t="inlineStr"/>
+      <c r="H712" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I712" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J712" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K712" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="713">
       <c r="A713" s="2" t="inlineStr">
@@ -31318,10 +33138,20 @@
       <c r="G713" s="2" t="n">
         <v>1.9</v>
       </c>
-      <c r="H713" s="6" t="inlineStr"/>
-      <c r="I713" s="6" t="inlineStr"/>
-      <c r="J713" s="6" t="inlineStr"/>
-      <c r="K713" s="6" t="inlineStr"/>
+      <c r="H713" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I713" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J713" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K713" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="714">
       <c r="A714" s="2" t="inlineStr">
@@ -31357,10 +33187,20 @@
       <c r="G714" s="2" t="n">
         <v>4.1</v>
       </c>
-      <c r="H714" s="6" t="inlineStr"/>
-      <c r="I714" s="6" t="inlineStr"/>
-      <c r="J714" s="6" t="inlineStr"/>
-      <c r="K714" s="6" t="inlineStr"/>
+      <c r="H714" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I714" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J714" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K714" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="715">
       <c r="A715" s="2" t="inlineStr">
@@ -31396,10 +33236,20 @@
       <c r="G715" s="2" t="n">
         <v>1.86</v>
       </c>
-      <c r="H715" s="6" t="inlineStr"/>
-      <c r="I715" s="6" t="inlineStr"/>
-      <c r="J715" s="6" t="inlineStr"/>
-      <c r="K715" s="6" t="inlineStr"/>
+      <c r="H715" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I715" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J715" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K715" s="4" t="n">
+        <v>86</v>
+      </c>
     </row>
     <row r="716">
       <c r="A716" s="2" t="inlineStr">
@@ -31591,10 +33441,20 @@
       <c r="G720" s="2" t="n">
         <v>10.5</v>
       </c>
-      <c r="H720" s="6" t="inlineStr"/>
-      <c r="I720" s="6" t="inlineStr"/>
-      <c r="J720" s="6" t="inlineStr"/>
-      <c r="K720" s="6" t="inlineStr"/>
+      <c r="H720" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I720" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J720" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K720" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="721">
       <c r="A721" s="2" t="inlineStr">
@@ -31630,10 +33490,20 @@
       <c r="G721" s="2" t="n">
         <v>2.3</v>
       </c>
-      <c r="H721" s="6" t="inlineStr"/>
-      <c r="I721" s="6" t="inlineStr"/>
-      <c r="J721" s="6" t="inlineStr"/>
-      <c r="K721" s="6" t="inlineStr"/>
+      <c r="H721" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I721" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J721" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K721" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="722">
       <c r="A722" s="2" t="inlineStr">
@@ -31825,10 +33695,20 @@
       <c r="G726" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="H726" s="6" t="inlineStr"/>
-      <c r="I726" s="6" t="inlineStr"/>
-      <c r="J726" s="6" t="inlineStr"/>
-      <c r="K726" s="6" t="inlineStr"/>
+      <c r="H726" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I726" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J726" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K726" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="727">
       <c r="A727" s="2" t="inlineStr">
@@ -31864,10 +33744,20 @@
       <c r="G727" s="2" t="n">
         <v>2.18</v>
       </c>
-      <c r="H727" s="6" t="inlineStr"/>
-      <c r="I727" s="6" t="inlineStr"/>
-      <c r="J727" s="6" t="inlineStr"/>
-      <c r="K727" s="6" t="inlineStr"/>
+      <c r="H727" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I727" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J727" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K727" s="4" t="n">
+        <v>118</v>
+      </c>
     </row>
     <row r="728">
       <c r="A728" s="2" t="inlineStr">
@@ -32020,10 +33910,20 @@
       <c r="G731" s="2" t="n">
         <v>3.95</v>
       </c>
-      <c r="H731" s="6" t="inlineStr"/>
-      <c r="I731" s="6" t="inlineStr"/>
-      <c r="J731" s="6" t="inlineStr"/>
-      <c r="K731" s="6" t="inlineStr"/>
+      <c r="H731" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I731" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J731" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K731" s="5" t="n">
+        <v>-295</v>
+      </c>
     </row>
     <row r="732">
       <c r="A732" s="2" t="inlineStr">
@@ -32059,10 +33959,20 @@
       <c r="G732" s="2" t="n">
         <v>4.5</v>
       </c>
-      <c r="H732" s="6" t="inlineStr"/>
-      <c r="I732" s="6" t="inlineStr"/>
-      <c r="J732" s="6" t="inlineStr"/>
-      <c r="K732" s="6" t="inlineStr"/>
+      <c r="H732" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I732" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J732" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K732" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="733">
       <c r="A733" s="2" t="inlineStr">
@@ -32176,10 +34086,20 @@
       <c r="G735" s="2" t="n">
         <v>4.3</v>
       </c>
-      <c r="H735" s="6" t="inlineStr"/>
-      <c r="I735" s="6" t="inlineStr"/>
-      <c r="J735" s="6" t="inlineStr"/>
-      <c r="K735" s="6" t="inlineStr"/>
+      <c r="H735" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I735" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J735" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K735" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="736">
       <c r="A736" s="2" t="inlineStr">
@@ -32293,10 +34213,20 @@
       <c r="G738" s="2" t="n">
         <v>4.1</v>
       </c>
-      <c r="H738" s="6" t="inlineStr"/>
-      <c r="I738" s="6" t="inlineStr"/>
-      <c r="J738" s="6" t="inlineStr"/>
-      <c r="K738" s="6" t="inlineStr"/>
+      <c r="H738" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I738" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J738" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K738" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="739">
       <c r="A739" s="2" t="inlineStr">
@@ -32332,10 +34262,20 @@
       <c r="G739" s="2" t="n">
         <v>1.83</v>
       </c>
-      <c r="H739" s="6" t="inlineStr"/>
-      <c r="I739" s="6" t="inlineStr"/>
-      <c r="J739" s="6" t="inlineStr"/>
-      <c r="K739" s="6" t="inlineStr"/>
+      <c r="H739" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I739" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J739" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K739" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="740">
       <c r="A740" s="2" t="inlineStr">
@@ -32371,10 +34311,20 @@
       <c r="G740" s="2" t="n">
         <v>4.4</v>
       </c>
-      <c r="H740" s="6" t="inlineStr"/>
-      <c r="I740" s="6" t="inlineStr"/>
-      <c r="J740" s="6" t="inlineStr"/>
-      <c r="K740" s="6" t="inlineStr"/>
+      <c r="H740" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I740" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J740" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K740" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="741">
       <c r="A741" s="2" t="inlineStr">
@@ -32410,10 +34360,20 @@
       <c r="G741" s="2" t="n">
         <v>4.1</v>
       </c>
-      <c r="H741" s="6" t="inlineStr"/>
-      <c r="I741" s="6" t="inlineStr"/>
-      <c r="J741" s="6" t="inlineStr"/>
-      <c r="K741" s="6" t="inlineStr"/>
+      <c r="H741" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I741" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J741" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K741" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="742">
       <c r="A742" s="2" t="inlineStr">
@@ -32488,10 +34448,20 @@
       <c r="G743" s="2" t="n">
         <v>4.1</v>
       </c>
-      <c r="H743" s="6" t="inlineStr"/>
-      <c r="I743" s="6" t="inlineStr"/>
-      <c r="J743" s="6" t="inlineStr"/>
-      <c r="K743" s="6" t="inlineStr"/>
+      <c r="H743" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I743" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J743" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K743" s="5" t="n">
+        <v>-310</v>
+      </c>
     </row>
     <row r="744">
       <c r="A744" s="2" t="inlineStr">
@@ -32527,10 +34497,20 @@
       <c r="G744" s="2" t="n">
         <v>3.8</v>
       </c>
-      <c r="H744" s="6" t="inlineStr"/>
-      <c r="I744" s="6" t="inlineStr"/>
-      <c r="J744" s="6" t="inlineStr"/>
-      <c r="K744" s="6" t="inlineStr"/>
+      <c r="H744" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I744" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J744" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K744" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="745">
       <c r="A745" s="2" t="inlineStr">
@@ -32566,10 +34546,20 @@
       <c r="G745" s="2" t="n">
         <v>1.86</v>
       </c>
-      <c r="H745" s="6" t="inlineStr"/>
-      <c r="I745" s="6" t="inlineStr"/>
-      <c r="J745" s="6" t="inlineStr"/>
-      <c r="K745" s="6" t="inlineStr"/>
+      <c r="H745" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I745" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J745" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K745" s="4" t="n">
+        <v>86</v>
+      </c>
     </row>
     <row r="746">
       <c r="A746" s="2" t="inlineStr">
@@ -32605,10 +34595,20 @@
       <c r="G746" s="2" t="n">
         <v>4.2</v>
       </c>
-      <c r="H746" s="6" t="inlineStr"/>
-      <c r="I746" s="6" t="inlineStr"/>
-      <c r="J746" s="6" t="inlineStr"/>
-      <c r="K746" s="6" t="inlineStr"/>
+      <c r="H746" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I746" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J746" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K746" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="747">
       <c r="A747" s="2" t="inlineStr">
@@ -32839,10 +34839,20 @@
       <c r="G752" s="2" t="n">
         <v>3.95</v>
       </c>
-      <c r="H752" s="6" t="inlineStr"/>
-      <c r="I752" s="6" t="inlineStr"/>
-      <c r="J752" s="6" t="inlineStr"/>
-      <c r="K752" s="6" t="inlineStr"/>
+      <c r="H752" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I752" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J752" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K752" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="753">
       <c r="A753" s="2" t="inlineStr">
@@ -32878,10 +34888,20 @@
       <c r="G753" s="2" t="n">
         <v>4.2</v>
       </c>
-      <c r="H753" s="6" t="inlineStr"/>
-      <c r="I753" s="6" t="inlineStr"/>
-      <c r="J753" s="6" t="inlineStr"/>
-      <c r="K753" s="6" t="inlineStr"/>
+      <c r="H753" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I753" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J753" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K753" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="754">
       <c r="A754" s="2" t="inlineStr">
@@ -32917,10 +34937,20 @@
       <c r="G754" s="2" t="n">
         <v>1.93</v>
       </c>
-      <c r="H754" s="6" t="inlineStr"/>
-      <c r="I754" s="6" t="inlineStr"/>
-      <c r="J754" s="6" t="inlineStr"/>
-      <c r="K754" s="6" t="inlineStr"/>
+      <c r="H754" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I754" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J754" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K754" s="4" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="755">
       <c r="A755" s="2" t="inlineStr">
@@ -32995,10 +35025,20 @@
       <c r="G756" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="H756" s="6" t="inlineStr"/>
-      <c r="I756" s="6" t="inlineStr"/>
-      <c r="J756" s="6" t="inlineStr"/>
-      <c r="K756" s="6" t="inlineStr"/>
+      <c r="H756" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I756" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J756" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K756" s="5" t="n">
+        <v>-250</v>
+      </c>
     </row>
     <row r="757">
       <c r="A757" s="2" t="inlineStr">
@@ -33034,10 +35074,20 @@
       <c r="G757" s="2" t="n">
         <v>2.08</v>
       </c>
-      <c r="H757" s="6" t="inlineStr"/>
-      <c r="I757" s="6" t="inlineStr"/>
-      <c r="J757" s="6" t="inlineStr"/>
-      <c r="K757" s="6" t="inlineStr"/>
+      <c r="H757" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I757" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J757" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K757" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="758">
       <c r="A758" s="2" t="inlineStr">
@@ -33112,10 +35162,20 @@
       <c r="G759" s="2" t="n">
         <v>3.65</v>
       </c>
-      <c r="H759" s="6" t="inlineStr"/>
-      <c r="I759" s="6" t="inlineStr"/>
-      <c r="J759" s="6" t="inlineStr"/>
-      <c r="K759" s="6" t="inlineStr"/>
+      <c r="H759" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I759" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J759" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K759" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="760">
       <c r="A760" s="2" t="inlineStr">
@@ -33151,10 +35211,20 @@
       <c r="G760" s="2" t="n">
         <v>1.94</v>
       </c>
-      <c r="H760" s="6" t="inlineStr"/>
-      <c r="I760" s="6" t="inlineStr"/>
-      <c r="J760" s="6" t="inlineStr"/>
-      <c r="K760" s="6" t="inlineStr"/>
+      <c r="H760" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I760" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J760" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K760" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="761">
       <c r="A761" s="2" t="inlineStr">
@@ -33190,10 +35260,20 @@
       <c r="G761" s="2" t="n">
         <v>4.3</v>
       </c>
-      <c r="H761" s="6" t="inlineStr"/>
-      <c r="I761" s="6" t="inlineStr"/>
-      <c r="J761" s="6" t="inlineStr"/>
-      <c r="K761" s="6" t="inlineStr"/>
+      <c r="H761" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I761" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J761" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K761" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="762">
       <c r="A762" s="2" t="inlineStr">
@@ -33385,10 +35465,20 @@
       <c r="G766" s="2" t="n">
         <v>3.95</v>
       </c>
-      <c r="H766" s="6" t="inlineStr"/>
-      <c r="I766" s="6" t="inlineStr"/>
-      <c r="J766" s="6" t="inlineStr"/>
-      <c r="K766" s="6" t="inlineStr"/>
+      <c r="H766" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I766" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J766" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K766" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="767">
       <c r="A767" s="2" t="inlineStr">
@@ -33424,10 +35514,20 @@
       <c r="G767" s="2" t="n">
         <v>2.06</v>
       </c>
-      <c r="H767" s="6" t="inlineStr"/>
-      <c r="I767" s="6" t="inlineStr"/>
-      <c r="J767" s="6" t="inlineStr"/>
-      <c r="K767" s="6" t="inlineStr"/>
+      <c r="H767" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I767" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J767" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K767" s="4" t="n">
+        <v>106</v>
+      </c>
     </row>
     <row r="768">
       <c r="A768" s="2" t="inlineStr">
@@ -33463,10 +35563,20 @@
       <c r="G768" s="2" t="n">
         <v>10.5</v>
       </c>
-      <c r="H768" s="6" t="inlineStr"/>
-      <c r="I768" s="6" t="inlineStr"/>
-      <c r="J768" s="6" t="inlineStr"/>
-      <c r="K768" s="6" t="inlineStr"/>
+      <c r="H768" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I768" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J768" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K768" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="769">
       <c r="A769" s="2" t="inlineStr">
@@ -33502,10 +35612,20 @@
       <c r="G769" s="2" t="n">
         <v>2.3</v>
       </c>
-      <c r="H769" s="6" t="inlineStr"/>
-      <c r="I769" s="6" t="inlineStr"/>
-      <c r="J769" s="6" t="inlineStr"/>
-      <c r="K769" s="6" t="inlineStr"/>
+      <c r="H769" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I769" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J769" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K769" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="770">
       <c r="A770" s="2" t="inlineStr">
@@ -33541,10 +35661,20 @@
       <c r="G770" s="2" t="n">
         <v>3.75</v>
       </c>
-      <c r="H770" s="6" t="inlineStr"/>
-      <c r="I770" s="6" t="inlineStr"/>
-      <c r="J770" s="6" t="inlineStr"/>
-      <c r="K770" s="6" t="inlineStr"/>
+      <c r="H770" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I770" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J770" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K770" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="771">
       <c r="A771" s="2" t="inlineStr">
@@ -33580,10 +35710,20 @@
       <c r="G771" s="2" t="n">
         <v>1.83</v>
       </c>
-      <c r="H771" s="6" t="inlineStr"/>
-      <c r="I771" s="6" t="inlineStr"/>
-      <c r="J771" s="6" t="inlineStr"/>
-      <c r="K771" s="6" t="inlineStr"/>
+      <c r="H771" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I771" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J771" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K771" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="772">
       <c r="A772" s="2" t="inlineStr">
@@ -33697,10 +35837,20 @@
       <c r="G774" s="2" t="n">
         <v>4.2</v>
       </c>
-      <c r="H774" s="6" t="inlineStr"/>
-      <c r="I774" s="6" t="inlineStr"/>
-      <c r="J774" s="6" t="inlineStr"/>
-      <c r="K774" s="6" t="inlineStr"/>
+      <c r="H774" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I774" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J774" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K774" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="775">
       <c r="A775" s="2" t="inlineStr">
@@ -33736,10 +35886,20 @@
       <c r="G775" s="2" t="n">
         <v>4.4</v>
       </c>
-      <c r="H775" s="6" t="inlineStr"/>
-      <c r="I775" s="6" t="inlineStr"/>
-      <c r="J775" s="6" t="inlineStr"/>
-      <c r="K775" s="6" t="inlineStr"/>
+      <c r="H775" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I775" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J775" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K775" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="776">
       <c r="A776" s="2" t="inlineStr">
@@ -33775,10 +35935,20 @@
       <c r="G776" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="H776" s="6" t="inlineStr"/>
-      <c r="I776" s="6" t="inlineStr"/>
-      <c r="J776" s="6" t="inlineStr"/>
-      <c r="K776" s="6" t="inlineStr"/>
+      <c r="H776" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I776" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J776" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K776" s="5" t="n">
+        <v>-300</v>
+      </c>
     </row>
     <row r="777">
       <c r="A777" s="2" t="inlineStr">
@@ -33814,10 +35984,20 @@
       <c r="G777" s="2" t="n">
         <v>10.5</v>
       </c>
-      <c r="H777" s="6" t="inlineStr"/>
-      <c r="I777" s="6" t="inlineStr"/>
-      <c r="J777" s="6" t="inlineStr"/>
-      <c r="K777" s="6" t="inlineStr"/>
+      <c r="H777" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I777" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J777" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K777" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="778">
       <c r="A778" s="2" t="inlineStr">
@@ -33853,10 +36033,20 @@
       <c r="G778" s="2" t="n">
         <v>3.35</v>
       </c>
-      <c r="H778" s="6" t="inlineStr"/>
-      <c r="I778" s="6" t="inlineStr"/>
-      <c r="J778" s="6" t="inlineStr"/>
-      <c r="K778" s="6" t="inlineStr"/>
+      <c r="H778" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I778" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J778" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K778" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="779">
       <c r="A779" s="2" t="inlineStr">
@@ -33892,10 +36082,20 @@
       <c r="G779" s="2" t="n">
         <v>2.6</v>
       </c>
-      <c r="H779" s="6" t="inlineStr"/>
-      <c r="I779" s="6" t="inlineStr"/>
-      <c r="J779" s="6" t="inlineStr"/>
-      <c r="K779" s="6" t="inlineStr"/>
+      <c r="H779" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I779" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J779" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K779" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="780">
       <c r="A780" s="2" t="inlineStr">
@@ -33931,10 +36131,20 @@
       <c r="G780" s="2" t="n">
         <v>2.42</v>
       </c>
-      <c r="H780" s="6" t="inlineStr"/>
-      <c r="I780" s="6" t="inlineStr"/>
-      <c r="J780" s="6" t="inlineStr"/>
-      <c r="K780" s="6" t="inlineStr"/>
+      <c r="H780" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I780" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J780" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K780" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="781">
       <c r="A781" s="2" t="inlineStr">
@@ -34087,10 +36297,20 @@
       <c r="G784" s="2" t="n">
         <v>10.5</v>
       </c>
-      <c r="H784" s="6" t="inlineStr"/>
-      <c r="I784" s="6" t="inlineStr"/>
-      <c r="J784" s="6" t="inlineStr"/>
-      <c r="K784" s="6" t="inlineStr"/>
+      <c r="H784" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I784" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J784" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K784" s="5" t="n">
+        <v>-950</v>
+      </c>
     </row>
     <row r="785">
       <c r="A785" s="2" t="inlineStr">
@@ -34126,10 +36346,20 @@
       <c r="G785" s="2" t="n">
         <v>2.6</v>
       </c>
-      <c r="H785" s="6" t="inlineStr"/>
-      <c r="I785" s="6" t="inlineStr"/>
-      <c r="J785" s="6" t="inlineStr"/>
-      <c r="K785" s="6" t="inlineStr"/>
+      <c r="H785" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I785" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J785" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K785" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="786">
       <c r="A786" s="2" t="inlineStr">
@@ -34165,10 +36395,20 @@
       <c r="G786" s="2" t="n">
         <v>2.3</v>
       </c>
-      <c r="H786" s="6" t="inlineStr"/>
-      <c r="I786" s="6" t="inlineStr"/>
-      <c r="J786" s="6" t="inlineStr"/>
-      <c r="K786" s="6" t="inlineStr"/>
+      <c r="H786" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I786" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J786" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K786" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="787">
       <c r="A787" s="2" t="inlineStr">
@@ -34204,10 +36444,20 @@
       <c r="G787" s="2" t="n">
         <v>4.2</v>
       </c>
-      <c r="H787" s="6" t="inlineStr"/>
-      <c r="I787" s="6" t="inlineStr"/>
-      <c r="J787" s="6" t="inlineStr"/>
-      <c r="K787" s="6" t="inlineStr"/>
+      <c r="H787" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I787" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J787" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K787" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="788">
       <c r="A788" s="2" t="inlineStr">
@@ -34243,10 +36493,20 @@
       <c r="G788" s="2" t="n">
         <v>1.87</v>
       </c>
-      <c r="H788" s="6" t="inlineStr"/>
-      <c r="I788" s="6" t="inlineStr"/>
-      <c r="J788" s="6" t="inlineStr"/>
-      <c r="K788" s="6" t="inlineStr"/>
+      <c r="H788" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I788" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J788" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K788" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="789">
       <c r="A789" s="2" t="inlineStr">
@@ -34321,10 +36581,20 @@
       <c r="G790" s="2" t="n">
         <v>4.5</v>
       </c>
-      <c r="H790" s="6" t="inlineStr"/>
-      <c r="I790" s="6" t="inlineStr"/>
-      <c r="J790" s="6" t="inlineStr"/>
-      <c r="K790" s="6" t="inlineStr"/>
+      <c r="H790" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I790" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J790" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K790" s="5" t="n">
+        <v>-350</v>
+      </c>
     </row>
     <row r="791">
       <c r="A791" s="2" t="inlineStr">
@@ -34711,10 +36981,20 @@
       <c r="G800" s="2" t="n">
         <v>3.95</v>
       </c>
-      <c r="H800" s="6" t="inlineStr"/>
-      <c r="I800" s="6" t="inlineStr"/>
-      <c r="J800" s="6" t="inlineStr"/>
-      <c r="K800" s="6" t="inlineStr"/>
+      <c r="H800" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I800" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J800" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K800" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="801">
       <c r="A801" s="2" t="inlineStr">
@@ -34750,10 +37030,20 @@
       <c r="G801" s="2" t="n">
         <v>1.88</v>
       </c>
-      <c r="H801" s="6" t="inlineStr"/>
-      <c r="I801" s="6" t="inlineStr"/>
-      <c r="J801" s="6" t="inlineStr"/>
-      <c r="K801" s="6" t="inlineStr"/>
+      <c r="H801" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I801" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J801" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K801" s="4" t="n">
+        <v>88</v>
+      </c>
     </row>
     <row r="802">
       <c r="A802" s="2" t="inlineStr">
@@ -34789,10 +37079,20 @@
       <c r="G802" s="2" t="n">
         <v>4.5</v>
       </c>
-      <c r="H802" s="6" t="inlineStr"/>
-      <c r="I802" s="6" t="inlineStr"/>
-      <c r="J802" s="6" t="inlineStr"/>
-      <c r="K802" s="6" t="inlineStr"/>
+      <c r="H802" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I802" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J802" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K802" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="803">
       <c r="A803" s="2" t="inlineStr">
@@ -34828,10 +37128,20 @@
       <c r="G803" s="2" t="n">
         <v>4.4</v>
       </c>
-      <c r="H803" s="6" t="inlineStr"/>
-      <c r="I803" s="6" t="inlineStr"/>
-      <c r="J803" s="6" t="inlineStr"/>
-      <c r="K803" s="6" t="inlineStr"/>
+      <c r="H803" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I803" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J803" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K803" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="804">
       <c r="A804" s="2" t="inlineStr">
@@ -34867,10 +37177,20 @@
       <c r="G804" s="2" t="n">
         <v>4.1</v>
       </c>
-      <c r="H804" s="6" t="inlineStr"/>
-      <c r="I804" s="6" t="inlineStr"/>
-      <c r="J804" s="6" t="inlineStr"/>
-      <c r="K804" s="6" t="inlineStr"/>
+      <c r="H804" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I804" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J804" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K804" s="5" t="n">
+        <v>-310</v>
+      </c>
     </row>
     <row r="805">
       <c r="A805" s="2" t="inlineStr">
@@ -35413,10 +37733,20 @@
       <c r="G818" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="H818" s="6" t="inlineStr"/>
-      <c r="I818" s="6" t="inlineStr"/>
-      <c r="J818" s="6" t="inlineStr"/>
-      <c r="K818" s="6" t="inlineStr"/>
+      <c r="H818" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I818" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J818" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K818" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="819">
       <c r="A819" s="2" t="inlineStr">
@@ -35452,10 +37782,20 @@
       <c r="G819" s="2" t="n">
         <v>2.16</v>
       </c>
-      <c r="H819" s="6" t="inlineStr"/>
-      <c r="I819" s="6" t="inlineStr"/>
-      <c r="J819" s="6" t="inlineStr"/>
-      <c r="K819" s="6" t="inlineStr"/>
+      <c r="H819" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I819" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J819" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K819" s="4" t="n">
+        <v>116</v>
+      </c>
     </row>
     <row r="820">
       <c r="A820" s="2" t="inlineStr">
@@ -35491,10 +37831,20 @@
       <c r="G820" s="2" t="n">
         <v>19.5</v>
       </c>
-      <c r="H820" s="6" t="inlineStr"/>
-      <c r="I820" s="6" t="inlineStr"/>
-      <c r="J820" s="6" t="inlineStr"/>
-      <c r="K820" s="6" t="inlineStr"/>
+      <c r="H820" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I820" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J820" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K820" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="821">
       <c r="A821" s="2" t="inlineStr">
@@ -35647,10 +37997,20 @@
       <c r="G824" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="H824" s="6" t="inlineStr"/>
-      <c r="I824" s="6" t="inlineStr"/>
-      <c r="J824" s="6" t="inlineStr"/>
-      <c r="K824" s="6" t="inlineStr"/>
+      <c r="H824" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I824" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J824" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K824" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="825">
       <c r="A825" s="2" t="inlineStr">
@@ -35686,10 +38046,20 @@
       <c r="G825" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="H825" s="6" t="inlineStr"/>
-      <c r="I825" s="6" t="inlineStr"/>
-      <c r="J825" s="6" t="inlineStr"/>
-      <c r="K825" s="6" t="inlineStr"/>
+      <c r="H825" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I825" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J825" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K825" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="826">
       <c r="A826" s="2" t="inlineStr">
@@ -35725,10 +38095,20 @@
       <c r="G826" s="2" t="n">
         <v>2.14</v>
       </c>
-      <c r="H826" s="6" t="inlineStr"/>
-      <c r="I826" s="6" t="inlineStr"/>
-      <c r="J826" s="6" t="inlineStr"/>
-      <c r="K826" s="6" t="inlineStr"/>
+      <c r="H826" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I826" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J826" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K826" s="4" t="n">
+        <v>114</v>
+      </c>
     </row>
     <row r="827">
       <c r="A827" s="2" t="inlineStr">
@@ -35764,10 +38144,20 @@
       <c r="G827" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="H827" s="6" t="inlineStr"/>
-      <c r="I827" s="6" t="inlineStr"/>
-      <c r="J827" s="6" t="inlineStr"/>
-      <c r="K827" s="6" t="inlineStr"/>
+      <c r="H827" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I827" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J827" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K827" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="828">
       <c r="A828" s="2" t="inlineStr">
@@ -35881,10 +38271,20 @@
       <c r="G830" s="2" t="n">
         <v>3.95</v>
       </c>
-      <c r="H830" s="6" t="inlineStr"/>
-      <c r="I830" s="6" t="inlineStr"/>
-      <c r="J830" s="6" t="inlineStr"/>
-      <c r="K830" s="6" t="inlineStr"/>
+      <c r="H830" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I830" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J830" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K830" s="5" t="n">
+        <v>-295</v>
+      </c>
     </row>
     <row r="831">
       <c r="A831" s="2" t="inlineStr">
@@ -35920,10 +38320,20 @@
       <c r="G831" s="2" t="n">
         <v>2.08</v>
       </c>
-      <c r="H831" s="6" t="inlineStr"/>
-      <c r="I831" s="6" t="inlineStr"/>
-      <c r="J831" s="6" t="inlineStr"/>
-      <c r="K831" s="6" t="inlineStr"/>
+      <c r="H831" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I831" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J831" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K831" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="832">
       <c r="A832" s="2" t="inlineStr">
@@ -36037,10 +38447,20 @@
       <c r="G834" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="H834" s="6" t="inlineStr"/>
-      <c r="I834" s="6" t="inlineStr"/>
-      <c r="J834" s="6" t="inlineStr"/>
-      <c r="K834" s="6" t="inlineStr"/>
+      <c r="H834" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I834" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J834" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K834" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="835">
       <c r="A835" s="2" t="inlineStr">
@@ -36076,10 +38496,20 @@
       <c r="G835" s="2" t="n">
         <v>3.7</v>
       </c>
-      <c r="H835" s="6" t="inlineStr"/>
-      <c r="I835" s="6" t="inlineStr"/>
-      <c r="J835" s="6" t="inlineStr"/>
-      <c r="K835" s="6" t="inlineStr"/>
+      <c r="H835" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I835" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J835" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K835" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="836">
       <c r="A836" s="2" t="inlineStr">
@@ -36115,10 +38545,20 @@
       <c r="G836" s="2" t="n">
         <v>2.16</v>
       </c>
-      <c r="H836" s="6" t="inlineStr"/>
-      <c r="I836" s="6" t="inlineStr"/>
-      <c r="J836" s="6" t="inlineStr"/>
-      <c r="K836" s="6" t="inlineStr"/>
+      <c r="H836" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I836" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J836" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K836" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="837">
       <c r="A837" s="2" t="inlineStr">
@@ -36154,10 +38594,20 @@
       <c r="G837" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="H837" s="6" t="inlineStr"/>
-      <c r="I837" s="6" t="inlineStr"/>
-      <c r="J837" s="6" t="inlineStr"/>
-      <c r="K837" s="6" t="inlineStr"/>
+      <c r="H837" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I837" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J837" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K837" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="838">
       <c r="A838" s="2" t="inlineStr">
@@ -36193,10 +38643,20 @@
       <c r="G838" s="2" t="n">
         <v>2.04</v>
       </c>
-      <c r="H838" s="6" t="inlineStr"/>
-      <c r="I838" s="6" t="inlineStr"/>
-      <c r="J838" s="6" t="inlineStr"/>
-      <c r="K838" s="6" t="inlineStr"/>
+      <c r="H838" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I838" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J838" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K838" s="4" t="n">
+        <v>104</v>
+      </c>
     </row>
     <row r="839">
       <c r="A839" s="2" t="inlineStr">
@@ -36505,10 +38965,20 @@
       <c r="G846" s="2" t="n">
         <v>3.45</v>
       </c>
-      <c r="H846" s="6" t="inlineStr"/>
-      <c r="I846" s="6" t="inlineStr"/>
-      <c r="J846" s="6" t="inlineStr"/>
-      <c r="K846" s="6" t="inlineStr"/>
+      <c r="H846" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I846" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J846" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K846" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="847">
       <c r="A847" s="2" t="inlineStr">
@@ -36544,10 +39014,20 @@
       <c r="G847" s="2" t="n">
         <v>2.06</v>
       </c>
-      <c r="H847" s="6" t="inlineStr"/>
-      <c r="I847" s="6" t="inlineStr"/>
-      <c r="J847" s="6" t="inlineStr"/>
-      <c r="K847" s="6" t="inlineStr"/>
+      <c r="H847" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I847" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J847" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K847" s="4" t="n">
+        <v>106</v>
+      </c>
     </row>
     <row r="848">
       <c r="A848" s="2" t="inlineStr">
@@ -36583,10 +39063,20 @@
       <c r="G848" s="2" t="n">
         <v>3.55</v>
       </c>
-      <c r="H848" s="6" t="inlineStr"/>
-      <c r="I848" s="6" t="inlineStr"/>
-      <c r="J848" s="6" t="inlineStr"/>
-      <c r="K848" s="6" t="inlineStr"/>
+      <c r="H848" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I848" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J848" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K848" s="5" t="n">
+        <v>-255</v>
+      </c>
     </row>
     <row r="849">
       <c r="A849" s="2" t="inlineStr">
@@ -36622,10 +39112,20 @@
       <c r="G849" s="2" t="n">
         <v>2.32</v>
       </c>
-      <c r="H849" s="6" t="inlineStr"/>
-      <c r="I849" s="6" t="inlineStr"/>
-      <c r="J849" s="6" t="inlineStr"/>
-      <c r="K849" s="6" t="inlineStr"/>
+      <c r="H849" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I849" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J849" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K849" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="850">
       <c r="A850" s="2" t="inlineStr">
@@ -36700,10 +39200,20 @@
       <c r="G851" s="2" t="n">
         <v>4.1</v>
       </c>
-      <c r="H851" s="6" t="inlineStr"/>
-      <c r="I851" s="6" t="inlineStr"/>
-      <c r="J851" s="6" t="inlineStr"/>
-      <c r="K851" s="6" t="inlineStr"/>
+      <c r="H851" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I851" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J851" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K851" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="852">
       <c r="A852" s="2" t="inlineStr">
@@ -36739,10 +39249,20 @@
       <c r="G852" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="H852" s="6" t="inlineStr"/>
-      <c r="I852" s="6" t="inlineStr"/>
-      <c r="J852" s="6" t="inlineStr"/>
-      <c r="K852" s="6" t="inlineStr"/>
+      <c r="H852" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I852" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J852" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K852" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="853">
       <c r="A853" s="2" t="inlineStr">
@@ -36778,10 +39298,20 @@
       <c r="G853" s="2" t="n">
         <v>3.6</v>
       </c>
-      <c r="H853" s="6" t="inlineStr"/>
-      <c r="I853" s="6" t="inlineStr"/>
-      <c r="J853" s="6" t="inlineStr"/>
-      <c r="K853" s="6" t="inlineStr"/>
+      <c r="H853" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I853" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J853" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K853" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="854">
       <c r="A854" s="2" t="inlineStr">
@@ -36817,10 +39347,20 @@
       <c r="G854" s="2" t="n">
         <v>2.34</v>
       </c>
-      <c r="H854" s="6" t="inlineStr"/>
-      <c r="I854" s="6" t="inlineStr"/>
-      <c r="J854" s="6" t="inlineStr"/>
-      <c r="K854" s="6" t="inlineStr"/>
+      <c r="H854" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I854" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J854" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K854" s="4" t="n">
+        <v>134</v>
+      </c>
     </row>
     <row r="855">
       <c r="A855" s="2" t="inlineStr">
@@ -36856,10 +39396,20 @@
       <c r="G855" s="2" t="n">
         <v>2.2</v>
       </c>
-      <c r="H855" s="6" t="inlineStr"/>
-      <c r="I855" s="6" t="inlineStr"/>
-      <c r="J855" s="6" t="inlineStr"/>
-      <c r="K855" s="6" t="inlineStr"/>
+      <c r="H855" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I855" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J855" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K855" s="5" t="n">
+        <v>-120</v>
+      </c>
     </row>
     <row r="856">
       <c r="A856" s="2" t="inlineStr">
@@ -37090,10 +39640,20 @@
       <c r="G861" s="2" t="n">
         <v>10.5</v>
       </c>
-      <c r="H861" s="6" t="inlineStr"/>
-      <c r="I861" s="6" t="inlineStr"/>
-      <c r="J861" s="6" t="inlineStr"/>
-      <c r="K861" s="6" t="inlineStr"/>
+      <c r="H861" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I861" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J861" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K861" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="862">
       <c r="A862" s="2" t="inlineStr">
@@ -37129,10 +39689,20 @@
       <c r="G862" s="2" t="n">
         <v>3.55</v>
       </c>
-      <c r="H862" s="6" t="inlineStr"/>
-      <c r="I862" s="6" t="inlineStr"/>
-      <c r="J862" s="6" t="inlineStr"/>
-      <c r="K862" s="6" t="inlineStr"/>
+      <c r="H862" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I862" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J862" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K862" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="863">
       <c r="A863" s="2" t="inlineStr">
@@ -37168,10 +39738,20 @@
       <c r="G863" s="2" t="n">
         <v>2.46</v>
       </c>
-      <c r="H863" s="6" t="inlineStr"/>
-      <c r="I863" s="6" t="inlineStr"/>
-      <c r="J863" s="6" t="inlineStr"/>
-      <c r="K863" s="6" t="inlineStr"/>
+      <c r="H863" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I863" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J863" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K863" s="4" t="n">
+        <v>146</v>
+      </c>
     </row>
     <row r="864">
       <c r="A864" s="2" t="inlineStr">
@@ -37207,10 +39787,20 @@
       <c r="G864" s="2" t="n">
         <v>2.22</v>
       </c>
-      <c r="H864" s="6" t="inlineStr"/>
-      <c r="I864" s="6" t="inlineStr"/>
-      <c r="J864" s="6" t="inlineStr"/>
-      <c r="K864" s="6" t="inlineStr"/>
+      <c r="H864" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I864" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J864" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K864" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="865">
       <c r="A865" s="2" t="inlineStr">
@@ -37363,10 +39953,20 @@
       <c r="G868" s="2" t="n">
         <v>3.9</v>
       </c>
-      <c r="H868" s="6" t="inlineStr"/>
-      <c r="I868" s="6" t="inlineStr"/>
-      <c r="J868" s="6" t="inlineStr"/>
-      <c r="K868" s="6" t="inlineStr"/>
+      <c r="H868" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I868" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J868" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K868" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="869">
       <c r="A869" s="2" t="inlineStr">
@@ -37402,10 +40002,20 @@
       <c r="G869" s="2" t="n">
         <v>1.88</v>
       </c>
-      <c r="H869" s="6" t="inlineStr"/>
-      <c r="I869" s="6" t="inlineStr"/>
-      <c r="J869" s="6" t="inlineStr"/>
-      <c r="K869" s="6" t="inlineStr"/>
+      <c r="H869" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I869" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J869" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K869" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="870">
       <c r="A870" s="2" t="inlineStr">
@@ -37519,10 +40129,20 @@
       <c r="G872" s="2" t="n">
         <v>4.5</v>
       </c>
-      <c r="H872" s="6" t="inlineStr"/>
-      <c r="I872" s="6" t="inlineStr"/>
-      <c r="J872" s="6" t="inlineStr"/>
-      <c r="K872" s="6" t="inlineStr"/>
+      <c r="H872" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I872" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J872" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K872" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="873">
       <c r="A873" s="2" t="inlineStr">
@@ -37558,10 +40178,20 @@
       <c r="G873" s="2" t="n">
         <v>3.8</v>
       </c>
-      <c r="H873" s="6" t="inlineStr"/>
-      <c r="I873" s="6" t="inlineStr"/>
-      <c r="J873" s="6" t="inlineStr"/>
-      <c r="K873" s="6" t="inlineStr"/>
+      <c r="H873" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I873" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J873" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K873" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="874">
       <c r="A874" s="2" t="inlineStr">
@@ -37792,10 +40422,20 @@
       <c r="G879" s="2" t="n">
         <v>4.2</v>
       </c>
-      <c r="H879" s="6" t="inlineStr"/>
-      <c r="I879" s="6" t="inlineStr"/>
-      <c r="J879" s="6" t="inlineStr"/>
-      <c r="K879" s="6" t="inlineStr"/>
+      <c r="H879" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I879" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J879" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K879" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="880">
       <c r="A880" s="2" t="inlineStr">
@@ -37831,10 +40471,20 @@
       <c r="G880" s="2" t="n">
         <v>1.9</v>
       </c>
-      <c r="H880" s="6" t="inlineStr"/>
-      <c r="I880" s="6" t="inlineStr"/>
-      <c r="J880" s="6" t="inlineStr"/>
-      <c r="K880" s="6" t="inlineStr"/>
+      <c r="H880" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I880" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J880" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K880" s="4" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="881">
       <c r="A881" s="2" t="inlineStr">
@@ -38026,10 +40676,20 @@
       <c r="G885" s="2" t="n">
         <v>3.7</v>
       </c>
-      <c r="H885" s="6" t="inlineStr"/>
-      <c r="I885" s="6" t="inlineStr"/>
-      <c r="J885" s="6" t="inlineStr"/>
-      <c r="K885" s="6" t="inlineStr"/>
+      <c r="H885" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I885" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J885" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K885" s="5" t="n">
+        <v>-270</v>
+      </c>
     </row>
     <row r="886">
       <c r="A886" s="2" t="inlineStr">
@@ -38065,10 +40725,20 @@
       <c r="G886" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H886" s="6" t="inlineStr"/>
-      <c r="I886" s="6" t="inlineStr"/>
-      <c r="J886" s="6" t="inlineStr"/>
-      <c r="K886" s="6" t="inlineStr"/>
+      <c r="H886" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I886" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J886" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K886" s="4" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="887">
       <c r="A887" s="2" t="inlineStr">
@@ -38104,10 +40774,20 @@
       <c r="G887" s="2" t="n">
         <v>10.5</v>
       </c>
-      <c r="H887" s="6" t="inlineStr"/>
-      <c r="I887" s="6" t="inlineStr"/>
-      <c r="J887" s="6" t="inlineStr"/>
-      <c r="K887" s="6" t="inlineStr"/>
+      <c r="H887" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I887" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J887" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K887" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="888">
       <c r="A888" s="2" t="inlineStr">
@@ -38143,10 +40823,20 @@
       <c r="G888" s="2" t="n">
         <v>3.35</v>
       </c>
-      <c r="H888" s="6" t="inlineStr"/>
-      <c r="I888" s="6" t="inlineStr"/>
-      <c r="J888" s="6" t="inlineStr"/>
-      <c r="K888" s="6" t="inlineStr"/>
+      <c r="H888" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I888" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J888" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K888" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="889">
       <c r="A889" s="2" t="inlineStr">
@@ -38182,10 +40872,20 @@
       <c r="G889" s="2" t="n">
         <v>2.48</v>
       </c>
-      <c r="H889" s="6" t="inlineStr"/>
-      <c r="I889" s="6" t="inlineStr"/>
-      <c r="J889" s="6" t="inlineStr"/>
-      <c r="K889" s="6" t="inlineStr"/>
+      <c r="H889" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I889" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J889" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K889" s="4" t="n">
+        <v>148</v>
+      </c>
     </row>
     <row r="890">
       <c r="A890" s="2" t="inlineStr">
@@ -38338,10 +41038,20 @@
       <c r="G893" s="2" t="n">
         <v>3.75</v>
       </c>
-      <c r="H893" s="6" t="inlineStr"/>
-      <c r="I893" s="6" t="inlineStr"/>
-      <c r="J893" s="6" t="inlineStr"/>
-      <c r="K893" s="6" t="inlineStr"/>
+      <c r="H893" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I893" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J893" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K893" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="894">
       <c r="A894" s="2" t="inlineStr">
@@ -38377,10 +41087,20 @@
       <c r="G894" s="2" t="n">
         <v>2.12</v>
       </c>
-      <c r="H894" s="6" t="inlineStr"/>
-      <c r="I894" s="6" t="inlineStr"/>
-      <c r="J894" s="6" t="inlineStr"/>
-      <c r="K894" s="6" t="inlineStr"/>
+      <c r="H894" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I894" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J894" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K894" s="4" t="n">
+        <v>112</v>
+      </c>
     </row>
     <row r="895">
       <c r="A895" s="2" t="inlineStr">
@@ -38494,10 +41214,20 @@
       <c r="G897" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="H897" s="6" t="inlineStr"/>
-      <c r="I897" s="6" t="inlineStr"/>
-      <c r="J897" s="6" t="inlineStr"/>
-      <c r="K897" s="6" t="inlineStr"/>
+      <c r="H897" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I897" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J897" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K897" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="898">
       <c r="A898" s="2" t="inlineStr">
@@ -38533,10 +41263,20 @@
       <c r="G898" s="2" t="n">
         <v>3.35</v>
       </c>
-      <c r="H898" s="6" t="inlineStr"/>
-      <c r="I898" s="6" t="inlineStr"/>
-      <c r="J898" s="6" t="inlineStr"/>
-      <c r="K898" s="6" t="inlineStr"/>
+      <c r="H898" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I898" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J898" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K898" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="899">
       <c r="A899" s="2" t="inlineStr">
@@ -38572,10 +41312,20 @@
       <c r="G899" s="2" t="n">
         <v>2.42</v>
       </c>
-      <c r="H899" s="6" t="inlineStr"/>
-      <c r="I899" s="6" t="inlineStr"/>
-      <c r="J899" s="6" t="inlineStr"/>
-      <c r="K899" s="6" t="inlineStr"/>
+      <c r="H899" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I899" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J899" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K899" s="4" t="n">
+        <v>142</v>
+      </c>
     </row>
     <row r="900">
       <c r="A900" s="2" t="inlineStr">
@@ -38611,10 +41361,20 @@
       <c r="G900" s="2" t="n">
         <v>2.32</v>
       </c>
-      <c r="H900" s="6" t="inlineStr"/>
-      <c r="I900" s="6" t="inlineStr"/>
-      <c r="J900" s="6" t="inlineStr"/>
-      <c r="K900" s="6" t="inlineStr"/>
+      <c r="H900" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I900" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J900" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K900" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="901">
       <c r="A901" s="2" t="inlineStr">
@@ -38728,10 +41488,20 @@
       <c r="G903" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="H903" s="6" t="inlineStr"/>
-      <c r="I903" s="6" t="inlineStr"/>
-      <c r="J903" s="6" t="inlineStr"/>
-      <c r="K903" s="6" t="inlineStr"/>
+      <c r="H903" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I903" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J903" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K903" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="904">
       <c r="A904" s="2" t="inlineStr">
@@ -38767,10 +41537,20 @@
       <c r="G904" s="2" t="n">
         <v>3.65</v>
       </c>
-      <c r="H904" s="6" t="inlineStr"/>
-      <c r="I904" s="6" t="inlineStr"/>
-      <c r="J904" s="6" t="inlineStr"/>
-      <c r="K904" s="6" t="inlineStr"/>
+      <c r="H904" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I904" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J904" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K904" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="905">
       <c r="A905" s="2" t="inlineStr">
@@ -38806,10 +41586,20 @@
       <c r="G905" s="2" t="n">
         <v>2.44</v>
       </c>
-      <c r="H905" s="6" t="inlineStr"/>
-      <c r="I905" s="6" t="inlineStr"/>
-      <c r="J905" s="6" t="inlineStr"/>
-      <c r="K905" s="6" t="inlineStr"/>
+      <c r="H905" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I905" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J905" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K905" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="906">
       <c r="A906" s="2" t="inlineStr">
@@ -38845,10 +41635,20 @@
       <c r="G906" s="2" t="n">
         <v>2.3</v>
       </c>
-      <c r="H906" s="6" t="inlineStr"/>
-      <c r="I906" s="6" t="inlineStr"/>
-      <c r="J906" s="6" t="inlineStr"/>
-      <c r="K906" s="6" t="inlineStr"/>
+      <c r="H906" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I906" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J906" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K906" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="907">
       <c r="A907" s="2" t="inlineStr">
@@ -39001,10 +41801,20 @@
       <c r="G910" s="2" t="n">
         <v>3.8</v>
       </c>
-      <c r="H910" s="6" t="inlineStr"/>
-      <c r="I910" s="6" t="inlineStr"/>
-      <c r="J910" s="6" t="inlineStr"/>
-      <c r="K910" s="6" t="inlineStr"/>
+      <c r="H910" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I910" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J910" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K910" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="911">
       <c r="A911" s="2" t="inlineStr">
@@ -39040,10 +41850,20 @@
       <c r="G911" s="2" t="n">
         <v>2.1</v>
       </c>
-      <c r="H911" s="6" t="inlineStr"/>
-      <c r="I911" s="6" t="inlineStr"/>
-      <c r="J911" s="6" t="inlineStr"/>
-      <c r="K911" s="6" t="inlineStr"/>
+      <c r="H911" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I911" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J911" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K911" s="4" t="n">
+        <v>110</v>
+      </c>
     </row>
     <row r="912">
       <c r="A912" s="2" t="inlineStr">
@@ -39079,10 +41899,20 @@
       <c r="G912" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="H912" s="6" t="inlineStr"/>
-      <c r="I912" s="6" t="inlineStr"/>
-      <c r="J912" s="6" t="inlineStr"/>
-      <c r="K912" s="6" t="inlineStr"/>
+      <c r="H912" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I912" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J912" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K912" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="913">
       <c r="A913" s="2" t="inlineStr">
@@ -39118,10 +41948,20 @@
       <c r="G913" s="2" t="n">
         <v>4.3</v>
       </c>
-      <c r="H913" s="6" t="inlineStr"/>
-      <c r="I913" s="6" t="inlineStr"/>
-      <c r="J913" s="6" t="inlineStr"/>
-      <c r="K913" s="6" t="inlineStr"/>
+      <c r="H913" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I913" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J913" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K913" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="914">
       <c r="A914" s="2" t="inlineStr">
@@ -39157,10 +41997,20 @@
       <c r="G914" s="2" t="n">
         <v>1.94</v>
       </c>
-      <c r="H914" s="6" t="inlineStr"/>
-      <c r="I914" s="6" t="inlineStr"/>
-      <c r="J914" s="6" t="inlineStr"/>
-      <c r="K914" s="6" t="inlineStr"/>
+      <c r="H914" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I914" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J914" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K914" s="4" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="915">
       <c r="A915" s="2" t="inlineStr">
@@ -39430,10 +42280,20 @@
       <c r="G921" s="2" t="n">
         <v>11.5</v>
       </c>
-      <c r="H921" s="6" t="inlineStr"/>
-      <c r="I921" s="6" t="inlineStr"/>
-      <c r="J921" s="6" t="inlineStr"/>
-      <c r="K921" s="6" t="inlineStr"/>
+      <c r="H921" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I921" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J921" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K921" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="922">
       <c r="A922" s="2" t="inlineStr">
@@ -39469,10 +42329,20 @@
       <c r="G922" s="2" t="n">
         <v>3.95</v>
       </c>
-      <c r="H922" s="6" t="inlineStr"/>
-      <c r="I922" s="6" t="inlineStr"/>
-      <c r="J922" s="6" t="inlineStr"/>
-      <c r="K922" s="6" t="inlineStr"/>
+      <c r="H922" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I922" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J922" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K922" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="923">
       <c r="A923" s="2" t="inlineStr">
@@ -39508,10 +42378,20 @@
       <c r="G923" s="2" t="n">
         <v>2.34</v>
       </c>
-      <c r="H923" s="6" t="inlineStr"/>
-      <c r="I923" s="6" t="inlineStr"/>
-      <c r="J923" s="6" t="inlineStr"/>
-      <c r="K923" s="6" t="inlineStr"/>
+      <c r="H923" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I923" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J923" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K923" s="4" t="n">
+        <v>134</v>
+      </c>
     </row>
     <row r="924">
       <c r="A924" s="2" t="inlineStr">
@@ -39547,10 +42427,20 @@
       <c r="G924" s="2" t="n">
         <v>2.3</v>
       </c>
-      <c r="H924" s="6" t="inlineStr"/>
-      <c r="I924" s="6" t="inlineStr"/>
-      <c r="J924" s="6" t="inlineStr"/>
-      <c r="K924" s="6" t="inlineStr"/>
+      <c r="H924" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I924" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J924" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K924" s="5" t="n">
+        <v>-130</v>
+      </c>
     </row>
     <row r="925">
       <c r="A925" s="2" t="inlineStr">
@@ -39820,10 +42710,20 @@
       <c r="G931" s="2" t="n">
         <v>3.9</v>
       </c>
-      <c r="H931" s="6" t="inlineStr"/>
-      <c r="I931" s="6" t="inlineStr"/>
-      <c r="J931" s="6" t="inlineStr"/>
-      <c r="K931" s="6" t="inlineStr"/>
+      <c r="H931" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I931" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J931" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K931" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="932">
       <c r="A932" s="2" t="inlineStr">
@@ -39859,10 +42759,20 @@
       <c r="G932" s="2" t="n">
         <v>3.7</v>
       </c>
-      <c r="H932" s="6" t="inlineStr"/>
-      <c r="I932" s="6" t="inlineStr"/>
-      <c r="J932" s="6" t="inlineStr"/>
-      <c r="K932" s="6" t="inlineStr"/>
+      <c r="H932" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I932" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J932" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K932" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="933">
       <c r="A933" s="2" t="inlineStr">
@@ -39898,10 +42808,20 @@
       <c r="G933" s="2" t="n">
         <v>2.48</v>
       </c>
-      <c r="H933" s="6" t="inlineStr"/>
-      <c r="I933" s="6" t="inlineStr"/>
-      <c r="J933" s="6" t="inlineStr"/>
-      <c r="K933" s="6" t="inlineStr"/>
+      <c r="H933" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I933" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J933" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K933" s="5" t="n">
+        <v>-148</v>
+      </c>
     </row>
     <row r="934">
       <c r="A934" s="2" t="inlineStr">
@@ -39937,10 +42857,20 @@
       <c r="G934" s="2" t="n">
         <v>2.64</v>
       </c>
-      <c r="H934" s="6" t="inlineStr"/>
-      <c r="I934" s="6" t="inlineStr"/>
-      <c r="J934" s="6" t="inlineStr"/>
-      <c r="K934" s="6" t="inlineStr"/>
+      <c r="H934" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I934" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J934" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K934" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="935">
       <c r="A935" s="2" t="inlineStr">
@@ -39976,10 +42906,20 @@
       <c r="G935" s="2" t="n">
         <v>2.68</v>
       </c>
-      <c r="H935" s="6" t="inlineStr"/>
-      <c r="I935" s="6" t="inlineStr"/>
-      <c r="J935" s="6" t="inlineStr"/>
-      <c r="K935" s="6" t="inlineStr"/>
+      <c r="H935" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I935" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J935" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K935" s="5" t="n">
+        <v>-168</v>
+      </c>
     </row>
     <row r="936">
       <c r="A936" s="2" t="inlineStr">
@@ -40015,10 +42955,20 @@
       <c r="G936" s="2" t="n">
         <v>4.5</v>
       </c>
-      <c r="H936" s="6" t="inlineStr"/>
-      <c r="I936" s="6" t="inlineStr"/>
-      <c r="J936" s="6" t="inlineStr"/>
-      <c r="K936" s="6" t="inlineStr"/>
+      <c r="H936" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I936" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J936" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K936" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="937">
       <c r="A937" s="2" t="inlineStr">
@@ -40054,10 +43004,20 @@
       <c r="G937" s="2" t="n">
         <v>2.12</v>
       </c>
-      <c r="H937" s="6" t="inlineStr"/>
-      <c r="I937" s="6" t="inlineStr"/>
-      <c r="J937" s="6" t="inlineStr"/>
-      <c r="K937" s="6" t="inlineStr"/>
+      <c r="H937" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I937" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J937" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K937" s="4" t="n">
+        <v>112</v>
+      </c>
     </row>
     <row r="938">
       <c r="A938" s="2" t="inlineStr">
@@ -40093,10 +43053,20 @@
       <c r="G938" s="2" t="n">
         <v>2.3</v>
       </c>
-      <c r="H938" s="6" t="inlineStr"/>
-      <c r="I938" s="6" t="inlineStr"/>
-      <c r="J938" s="6" t="inlineStr"/>
-      <c r="K938" s="6" t="inlineStr"/>
+      <c r="H938" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I938" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J938" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K938" s="5" t="n">
+        <v>-130</v>
+      </c>
     </row>
     <row r="939">
       <c r="A939" s="2" t="inlineStr">
@@ -40210,10 +43180,20 @@
       <c r="G941" s="2" t="n">
         <v>3.75</v>
       </c>
-      <c r="H941" s="6" t="inlineStr"/>
-      <c r="I941" s="6" t="inlineStr"/>
-      <c r="J941" s="6" t="inlineStr"/>
-      <c r="K941" s="6" t="inlineStr"/>
+      <c r="H941" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I941" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J941" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K941" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="942">
       <c r="A942" s="2" t="inlineStr">
@@ -40249,10 +43229,20 @@
       <c r="G942" s="2" t="n">
         <v>2.12</v>
       </c>
-      <c r="H942" s="6" t="inlineStr"/>
-      <c r="I942" s="6" t="inlineStr"/>
-      <c r="J942" s="6" t="inlineStr"/>
-      <c r="K942" s="6" t="inlineStr"/>
+      <c r="H942" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I942" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J942" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K942" s="4" t="n">
+        <v>112</v>
+      </c>
     </row>
     <row r="943">
       <c r="A943" s="2" t="inlineStr">
@@ -40288,10 +43278,20 @@
       <c r="G943" s="2" t="n">
         <v>3.9</v>
       </c>
-      <c r="H943" s="6" t="inlineStr"/>
-      <c r="I943" s="6" t="inlineStr"/>
-      <c r="J943" s="6" t="inlineStr"/>
-      <c r="K943" s="6" t="inlineStr"/>
+      <c r="H943" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I943" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J943" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K943" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="944">
       <c r="A944" s="2" t="inlineStr">
@@ -40327,10 +43327,20 @@
       <c r="G944" s="2" t="n">
         <v>1.9</v>
       </c>
-      <c r="H944" s="6" t="inlineStr"/>
-      <c r="I944" s="6" t="inlineStr"/>
-      <c r="J944" s="6" t="inlineStr"/>
-      <c r="K944" s="6" t="inlineStr"/>
+      <c r="H944" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I944" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J944" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K944" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="945">
       <c r="A945" s="2" t="inlineStr">
@@ -40366,10 +43376,20 @@
       <c r="G945" s="2" t="n">
         <v>4.5</v>
       </c>
-      <c r="H945" s="6" t="inlineStr"/>
-      <c r="I945" s="6" t="inlineStr"/>
-      <c r="J945" s="6" t="inlineStr"/>
-      <c r="K945" s="6" t="inlineStr"/>
+      <c r="H945" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I945" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J945" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K945" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="946">
       <c r="A946" s="2" t="inlineStr">
@@ -40795,10 +43815,20 @@
       <c r="G956" s="2" t="n">
         <v>10.5</v>
       </c>
-      <c r="H956" s="6" t="inlineStr"/>
-      <c r="I956" s="6" t="inlineStr"/>
-      <c r="J956" s="6" t="inlineStr"/>
-      <c r="K956" s="6" t="inlineStr"/>
+      <c r="H956" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I956" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J956" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K956" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="957">
       <c r="A957" s="2" t="inlineStr">
@@ -40834,10 +43864,20 @@
       <c r="G957" s="2" t="n">
         <v>2.36</v>
       </c>
-      <c r="H957" s="6" t="inlineStr"/>
-      <c r="I957" s="6" t="inlineStr"/>
-      <c r="J957" s="6" t="inlineStr"/>
-      <c r="K957" s="6" t="inlineStr"/>
+      <c r="H957" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I957" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J957" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K957" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="958">
       <c r="A958" s="2" t="inlineStr">
@@ -41380,10 +44420,20 @@
       <c r="G971" s="2" t="n">
         <v>2.32</v>
       </c>
-      <c r="H971" s="6" t="inlineStr"/>
-      <c r="I971" s="6" t="inlineStr"/>
-      <c r="J971" s="6" t="inlineStr"/>
-      <c r="K971" s="6" t="inlineStr"/>
+      <c r="H971" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I971" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J971" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K971" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="972">
       <c r="A972" s="2" t="inlineStr">
@@ -41614,10 +44664,20 @@
       <c r="G977" s="2" t="n">
         <v>3.75</v>
       </c>
-      <c r="H977" s="6" t="inlineStr"/>
-      <c r="I977" s="6" t="inlineStr"/>
-      <c r="J977" s="6" t="inlineStr"/>
-      <c r="K977" s="6" t="inlineStr"/>
+      <c r="H977" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I977" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J977" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K977" s="5" t="n">
+        <v>-275</v>
+      </c>
     </row>
     <row r="978">
       <c r="A978" s="2" t="inlineStr">
@@ -41653,10 +44713,20 @@
       <c r="G978" s="2" t="n">
         <v>2.12</v>
       </c>
-      <c r="H978" s="6" t="inlineStr"/>
-      <c r="I978" s="6" t="inlineStr"/>
-      <c r="J978" s="6" t="inlineStr"/>
-      <c r="K978" s="6" t="inlineStr"/>
+      <c r="H978" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I978" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J978" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K978" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="979">
       <c r="A979" s="2" t="inlineStr">
@@ -41926,10 +44996,20 @@
       <c r="G985" s="2" t="n">
         <v>3.7</v>
       </c>
-      <c r="H985" s="6" t="inlineStr"/>
-      <c r="I985" s="6" t="inlineStr"/>
-      <c r="J985" s="6" t="inlineStr"/>
-      <c r="K985" s="6" t="inlineStr"/>
+      <c r="H985" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I985" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J985" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K985" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="986">
       <c r="A986" s="2" t="inlineStr">
@@ -41965,10 +45045,20 @@
       <c r="G986" s="2" t="n">
         <v>2.08</v>
       </c>
-      <c r="H986" s="6" t="inlineStr"/>
-      <c r="I986" s="6" t="inlineStr"/>
-      <c r="J986" s="6" t="inlineStr"/>
-      <c r="K986" s="6" t="inlineStr"/>
+      <c r="H986" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I986" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J986" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K986" s="4" t="n">
+        <v>108</v>
+      </c>
     </row>
     <row r="987">
       <c r="A987" s="2" t="inlineStr">
@@ -42121,10 +45211,20 @@
       <c r="G990" s="2" t="n">
         <v>11.5</v>
       </c>
-      <c r="H990" s="6" t="inlineStr"/>
-      <c r="I990" s="6" t="inlineStr"/>
-      <c r="J990" s="6" t="inlineStr"/>
-      <c r="K990" s="6" t="inlineStr"/>
+      <c r="H990" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I990" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J990" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K990" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="991">
       <c r="A991" s="2" t="inlineStr">
@@ -42160,10 +45260,20 @@
       <c r="G991" s="2" t="n">
         <v>4.2</v>
       </c>
-      <c r="H991" s="6" t="inlineStr"/>
-      <c r="I991" s="6" t="inlineStr"/>
-      <c r="J991" s="6" t="inlineStr"/>
-      <c r="K991" s="6" t="inlineStr"/>
+      <c r="H991" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I991" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J991" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K991" s="5" t="n">
+        <v>-320</v>
+      </c>
     </row>
     <row r="992">
       <c r="A992" s="2" t="inlineStr">
@@ -42199,10 +45309,20 @@
       <c r="G992" s="2" t="n">
         <v>2.3</v>
       </c>
-      <c r="H992" s="6" t="inlineStr"/>
-      <c r="I992" s="6" t="inlineStr"/>
-      <c r="J992" s="6" t="inlineStr"/>
-      <c r="K992" s="6" t="inlineStr"/>
+      <c r="H992" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I992" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J992" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K992" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="993">
       <c r="A993" s="2" t="inlineStr">
@@ -42238,10 +45358,20 @@
       <c r="G993" s="2" t="n">
         <v>2.54</v>
       </c>
-      <c r="H993" s="6" t="inlineStr"/>
-      <c r="I993" s="6" t="inlineStr"/>
-      <c r="J993" s="6" t="inlineStr"/>
-      <c r="K993" s="6" t="inlineStr"/>
+      <c r="H993" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I993" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J993" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K993" s="5" t="n">
+        <v>-154</v>
+      </c>
     </row>
     <row r="994">
       <c r="A994" s="2" t="inlineStr">
@@ -42277,10 +45407,20 @@
       <c r="G994" s="2" t="n">
         <v>15.5</v>
       </c>
-      <c r="H994" s="6" t="inlineStr"/>
-      <c r="I994" s="6" t="inlineStr"/>
-      <c r="J994" s="6" t="inlineStr"/>
-      <c r="K994" s="6" t="inlineStr"/>
+      <c r="H994" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I994" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J994" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K994" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="995">
       <c r="A995" s="2" t="inlineStr">
@@ -42316,10 +45456,20 @@
       <c r="G995" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="H995" s="6" t="inlineStr"/>
-      <c r="I995" s="6" t="inlineStr"/>
-      <c r="J995" s="6" t="inlineStr"/>
-      <c r="K995" s="6" t="inlineStr"/>
+      <c r="H995" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I995" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J995" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K995" s="5" t="n">
+        <v>-700</v>
+      </c>
     </row>
     <row r="996">
       <c r="A996" s="2" t="inlineStr">
@@ -42355,10 +45505,20 @@
       <c r="G996" s="2" t="n">
         <v>2.48</v>
       </c>
-      <c r="H996" s="6" t="inlineStr"/>
-      <c r="I996" s="6" t="inlineStr"/>
-      <c r="J996" s="6" t="inlineStr"/>
-      <c r="K996" s="6" t="inlineStr"/>
+      <c r="H996" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I996" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J996" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K996" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="997">
       <c r="A997" s="2" t="inlineStr">
@@ -42394,10 +45554,20 @@
       <c r="G997" s="2" t="n">
         <v>11.5</v>
       </c>
-      <c r="H997" s="6" t="inlineStr"/>
-      <c r="I997" s="6" t="inlineStr"/>
-      <c r="J997" s="6" t="inlineStr"/>
-      <c r="K997" s="6" t="inlineStr"/>
+      <c r="H997" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I997" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J997" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K997" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="998">
       <c r="A998" s="2" t="inlineStr">
@@ -42433,10 +45603,20 @@
       <c r="G998" s="2" t="n">
         <v>3.35</v>
       </c>
-      <c r="H998" s="6" t="inlineStr"/>
-      <c r="I998" s="6" t="inlineStr"/>
-      <c r="J998" s="6" t="inlineStr"/>
-      <c r="K998" s="6" t="inlineStr"/>
+      <c r="H998" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I998" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J998" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K998" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="999">
       <c r="A999" s="2" t="inlineStr">
@@ -42472,10 +45652,20 @@
       <c r="G999" s="2" t="n">
         <v>2.52</v>
       </c>
-      <c r="H999" s="6" t="inlineStr"/>
-      <c r="I999" s="6" t="inlineStr"/>
-      <c r="J999" s="6" t="inlineStr"/>
-      <c r="K999" s="6" t="inlineStr"/>
+      <c r="H999" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I999" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J999" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K999" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="1000">
       <c r="A1000" s="2" t="inlineStr">
@@ -42511,10 +45701,20 @@
       <c r="G1000" s="2" t="n">
         <v>2.36</v>
       </c>
-      <c r="H1000" s="6" t="inlineStr"/>
-      <c r="I1000" s="6" t="inlineStr"/>
-      <c r="J1000" s="6" t="inlineStr"/>
-      <c r="K1000" s="6" t="inlineStr"/>
+      <c r="H1000" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1000" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1000" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K1000" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="1001">
       <c r="A1001" s="2" t="inlineStr">
@@ -42550,10 +45750,20 @@
       <c r="G1001" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="H1001" s="6" t="inlineStr"/>
-      <c r="I1001" s="6" t="inlineStr"/>
-      <c r="J1001" s="6" t="inlineStr"/>
-      <c r="K1001" s="6" t="inlineStr"/>
+      <c r="H1001" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1001" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1001" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K1001" s="5" t="n">
+        <v>-300</v>
+      </c>
     </row>
     <row r="1002">
       <c r="A1002" s="2" t="inlineStr">
@@ -43291,10 +46501,20 @@
       <c r="G1020" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="H1020" s="6" t="inlineStr"/>
-      <c r="I1020" s="6" t="inlineStr"/>
-      <c r="J1020" s="6" t="inlineStr"/>
-      <c r="K1020" s="6" t="inlineStr"/>
+      <c r="H1020" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1020" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1020" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K1020" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="1021">
       <c r="A1021" s="2" t="inlineStr">
@@ -43330,10 +46550,20 @@
       <c r="G1021" s="2" t="n">
         <v>2.54</v>
       </c>
-      <c r="H1021" s="6" t="inlineStr"/>
-      <c r="I1021" s="6" t="inlineStr"/>
-      <c r="J1021" s="6" t="inlineStr"/>
-      <c r="K1021" s="6" t="inlineStr"/>
+      <c r="H1021" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1021" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1021" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K1021" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="1022">
       <c r="A1022" s="2" t="inlineStr">
@@ -43447,10 +46677,20 @@
       <c r="G1024" s="2" t="n">
         <v>3.75</v>
       </c>
-      <c r="H1024" s="6" t="inlineStr"/>
-      <c r="I1024" s="6" t="inlineStr"/>
-      <c r="J1024" s="6" t="inlineStr"/>
-      <c r="K1024" s="6" t="inlineStr"/>
+      <c r="H1024" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1024" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1024" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K1024" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="1025">
       <c r="A1025" s="2" t="inlineStr">
@@ -43486,10 +46726,20 @@
       <c r="G1025" s="2" t="n">
         <v>1.83</v>
       </c>
-      <c r="H1025" s="6" t="inlineStr"/>
-      <c r="I1025" s="6" t="inlineStr"/>
-      <c r="J1025" s="6" t="inlineStr"/>
-      <c r="K1025" s="6" t="inlineStr"/>
+      <c r="H1025" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1025" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1025" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K1025" s="4" t="n">
+        <v>83</v>
+      </c>
     </row>
     <row r="1026">
       <c r="A1026" s="2" t="inlineStr">
@@ -43525,10 +46775,20 @@
       <c r="G1026" s="2" t="n">
         <v>3.75</v>
       </c>
-      <c r="H1026" s="6" t="inlineStr"/>
-      <c r="I1026" s="6" t="inlineStr"/>
-      <c r="J1026" s="6" t="inlineStr"/>
-      <c r="K1026" s="6" t="inlineStr"/>
+      <c r="H1026" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1026" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1026" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K1026" s="5" t="n">
+        <v>-275</v>
+      </c>
     </row>
     <row r="1027">
       <c r="A1027" s="2" t="inlineStr">
@@ -43564,10 +46824,20 @@
       <c r="G1027" s="2" t="n">
         <v>2.18</v>
       </c>
-      <c r="H1027" s="6" t="inlineStr"/>
-      <c r="I1027" s="6" t="inlineStr"/>
-      <c r="J1027" s="6" t="inlineStr"/>
-      <c r="K1027" s="6" t="inlineStr"/>
+      <c r="H1027" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1027" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1027" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K1027" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="1028">
       <c r="A1028" s="2" t="inlineStr">
@@ -43603,10 +46873,20 @@
       <c r="G1028" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="H1028" s="6" t="inlineStr"/>
-      <c r="I1028" s="6" t="inlineStr"/>
-      <c r="J1028" s="6" t="inlineStr"/>
-      <c r="K1028" s="6" t="inlineStr"/>
+      <c r="H1028" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1028" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1028" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K1028" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="1029">
       <c r="A1029" s="2" t="inlineStr">
@@ -43798,10 +47078,20 @@
       <c r="G1033" s="2" t="n">
         <v>3.65</v>
       </c>
-      <c r="H1033" s="6" t="inlineStr"/>
-      <c r="I1033" s="6" t="inlineStr"/>
-      <c r="J1033" s="6" t="inlineStr"/>
-      <c r="K1033" s="6" t="inlineStr"/>
+      <c r="H1033" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1033" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1033" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K1033" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="1034">
       <c r="A1034" s="2" t="inlineStr">
@@ -43837,10 +47127,20 @@
       <c r="G1034" s="2" t="n">
         <v>2.04</v>
       </c>
-      <c r="H1034" s="6" t="inlineStr"/>
-      <c r="I1034" s="6" t="inlineStr"/>
-      <c r="J1034" s="6" t="inlineStr"/>
-      <c r="K1034" s="6" t="inlineStr"/>
+      <c r="H1034" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1034" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1034" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K1034" s="4" t="n">
+        <v>104</v>
+      </c>
     </row>
     <row r="1035">
       <c r="A1035" s="2" t="inlineStr">
@@ -44110,10 +47410,20 @@
       <c r="G1041" s="2" t="n">
         <v>4.3</v>
       </c>
-      <c r="H1041" s="6" t="inlineStr"/>
-      <c r="I1041" s="6" t="inlineStr"/>
-      <c r="J1041" s="6" t="inlineStr"/>
-      <c r="K1041" s="6" t="inlineStr"/>
+      <c r="H1041" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1041" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1041" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K1041" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="1042">
       <c r="A1042" s="2" t="inlineStr">
@@ -44149,10 +47459,20 @@
       <c r="G1042" s="2" t="n">
         <v>1.85</v>
       </c>
-      <c r="H1042" s="6" t="inlineStr"/>
-      <c r="I1042" s="6" t="inlineStr"/>
-      <c r="J1042" s="6" t="inlineStr"/>
-      <c r="K1042" s="6" t="inlineStr"/>
+      <c r="H1042" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1042" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1042" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K1042" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="1043">
       <c r="A1043" s="2" t="inlineStr">
@@ -44188,10 +47508,20 @@
       <c r="G1043" s="2" t="n">
         <v>3.55</v>
       </c>
-      <c r="H1043" s="6" t="inlineStr"/>
-      <c r="I1043" s="6" t="inlineStr"/>
-      <c r="J1043" s="6" t="inlineStr"/>
-      <c r="K1043" s="6" t="inlineStr"/>
+      <c r="H1043" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1043" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1043" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K1043" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="1044">
       <c r="A1044" s="2" t="inlineStr">
@@ -44227,10 +47557,20 @@
       <c r="G1044" s="2" t="n">
         <v>2.04</v>
       </c>
-      <c r="H1044" s="6" t="inlineStr"/>
-      <c r="I1044" s="6" t="inlineStr"/>
-      <c r="J1044" s="6" t="inlineStr"/>
-      <c r="K1044" s="6" t="inlineStr"/>
+      <c r="H1044" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1044" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1044" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K1044" s="4" t="n">
+        <v>104</v>
+      </c>
     </row>
     <row r="1045">
       <c r="A1045" s="2" t="inlineStr">
@@ -44266,10 +47606,20 @@
       <c r="G1045" s="2" t="n">
         <v>2.26</v>
       </c>
-      <c r="H1045" s="6" t="inlineStr"/>
-      <c r="I1045" s="6" t="inlineStr"/>
-      <c r="J1045" s="6" t="inlineStr"/>
-      <c r="K1045" s="6" t="inlineStr"/>
+      <c r="H1045" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1045" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1045" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K1045" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="1046">
       <c r="A1046" s="2" t="inlineStr">
@@ -44305,10 +47655,20 @@
       <c r="G1046" s="2" t="n">
         <v>3.7</v>
       </c>
-      <c r="H1046" s="6" t="inlineStr"/>
-      <c r="I1046" s="6" t="inlineStr"/>
-      <c r="J1046" s="6" t="inlineStr"/>
-      <c r="K1046" s="6" t="inlineStr"/>
+      <c r="H1046" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1046" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1046" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K1046" s="5" t="n">
+        <v>-270</v>
+      </c>
     </row>
     <row r="1047">
       <c r="A1047" s="2" t="inlineStr">
@@ -44344,10 +47704,20 @@
       <c r="G1047" s="2" t="n">
         <v>1.96</v>
       </c>
-      <c r="H1047" s="6" t="inlineStr"/>
-      <c r="I1047" s="6" t="inlineStr"/>
-      <c r="J1047" s="6" t="inlineStr"/>
-      <c r="K1047" s="6" t="inlineStr"/>
+      <c r="H1047" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1047" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1047" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K1047" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="1048">
       <c r="A1048" s="2" t="inlineStr">
@@ -44383,10 +47753,20 @@
       <c r="G1048" s="2" t="n">
         <v>2.6</v>
       </c>
-      <c r="H1048" s="6" t="inlineStr"/>
-      <c r="I1048" s="6" t="inlineStr"/>
-      <c r="J1048" s="6" t="inlineStr"/>
-      <c r="K1048" s="6" t="inlineStr"/>
+      <c r="H1048" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1048" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1048" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K1048" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="1049">
       <c r="A1049" s="2" t="inlineStr">
@@ -44461,10 +47841,20 @@
       <c r="G1050" s="2" t="n">
         <v>1.86</v>
       </c>
-      <c r="H1050" s="6" t="inlineStr"/>
-      <c r="I1050" s="6" t="inlineStr"/>
-      <c r="J1050" s="6" t="inlineStr"/>
-      <c r="K1050" s="6" t="inlineStr"/>
+      <c r="H1050" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1050" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1050" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K1050" s="4" t="n">
+        <v>86</v>
+      </c>
     </row>
     <row r="1051">
       <c r="A1051" s="2" t="inlineStr">
@@ -44500,10 +47890,20 @@
       <c r="G1051" s="2" t="n">
         <v>2.36</v>
       </c>
-      <c r="H1051" s="6" t="inlineStr"/>
-      <c r="I1051" s="6" t="inlineStr"/>
-      <c r="J1051" s="6" t="inlineStr"/>
-      <c r="K1051" s="6" t="inlineStr"/>
+      <c r="H1051" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1051" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1051" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K1051" s="5" t="n">
+        <v>-136</v>
+      </c>
     </row>
     <row r="1052">
       <c r="A1052" s="2" t="inlineStr">
@@ -44578,10 +47978,20 @@
       <c r="G1053" s="2" t="n">
         <v>4.4</v>
       </c>
-      <c r="H1053" s="6" t="inlineStr"/>
-      <c r="I1053" s="6" t="inlineStr"/>
-      <c r="J1053" s="6" t="inlineStr"/>
-      <c r="K1053" s="6" t="inlineStr"/>
+      <c r="H1053" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I1053" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1053" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K1053" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="1054">
       <c r="A1054" s="2" t="inlineStr">
@@ -44695,10 +48105,20 @@
       <c r="G1056" s="2" t="n">
         <v>3.75</v>
       </c>
-      <c r="H1056" s="6" t="inlineStr"/>
-      <c r="I1056" s="6" t="inlineStr"/>
-      <c r="J1056" s="6" t="inlineStr"/>
-      <c r="K1056" s="6" t="inlineStr"/>
+      <c r="H1056" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1056" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1056" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K1056" s="5" t="n">
+        <v>-275</v>
+      </c>
     </row>
     <row r="1057">
       <c r="A1057" s="2" t="inlineStr">
@@ -44734,10 +48154,20 @@
       <c r="G1057" s="2" t="n">
         <v>1.89</v>
       </c>
-      <c r="H1057" s="6" t="inlineStr"/>
-      <c r="I1057" s="6" t="inlineStr"/>
-      <c r="J1057" s="6" t="inlineStr"/>
-      <c r="K1057" s="6" t="inlineStr"/>
+      <c r="H1057" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1057" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1057" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K1057" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="1058">
       <c r="A1058" s="2" t="inlineStr">
@@ -44773,10 +48203,20 @@
       <c r="G1058" s="2" t="n">
         <v>3.65</v>
       </c>
-      <c r="H1058" s="6" t="inlineStr"/>
-      <c r="I1058" s="6" t="inlineStr"/>
-      <c r="J1058" s="6" t="inlineStr"/>
-      <c r="K1058" s="6" t="inlineStr"/>
+      <c r="H1058" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1058" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1058" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K1058" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="1059">
       <c r="A1059" s="2" t="inlineStr">
@@ -44812,10 +48252,20 @@
       <c r="G1059" s="2" t="n">
         <v>1.99</v>
       </c>
-      <c r="H1059" s="6" t="inlineStr"/>
-      <c r="I1059" s="6" t="inlineStr"/>
-      <c r="J1059" s="6" t="inlineStr"/>
-      <c r="K1059" s="6" t="inlineStr"/>
+      <c r="H1059" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1059" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1059" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K1059" s="4" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="1060">
       <c r="A1060" s="2" t="inlineStr">
@@ -44890,10 +48340,20 @@
       <c r="G1061" s="2" t="n">
         <v>3.95</v>
       </c>
-      <c r="H1061" s="6" t="inlineStr"/>
-      <c r="I1061" s="6" t="inlineStr"/>
-      <c r="J1061" s="6" t="inlineStr"/>
-      <c r="K1061" s="6" t="inlineStr"/>
+      <c r="H1061" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1061" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1061" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K1061" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="1062">
       <c r="A1062" s="2" t="inlineStr">
@@ -45124,10 +48584,20 @@
       <c r="G1067" s="2" t="n">
         <v>3.8</v>
       </c>
-      <c r="H1067" s="6" t="inlineStr"/>
-      <c r="I1067" s="6" t="inlineStr"/>
-      <c r="J1067" s="6" t="inlineStr"/>
-      <c r="K1067" s="6" t="inlineStr"/>
+      <c r="H1067" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I1067" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1067" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K1067" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="1068">
       <c r="A1068" s="2" t="inlineStr">
@@ -45163,10 +48633,20 @@
       <c r="G1068" s="2" t="n">
         <v>1.93</v>
       </c>
-      <c r="H1068" s="6" t="inlineStr"/>
-      <c r="I1068" s="6" t="inlineStr"/>
-      <c r="J1068" s="6" t="inlineStr"/>
-      <c r="K1068" s="6" t="inlineStr"/>
+      <c r="H1068" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I1068" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1068" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K1068" s="4" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="1069">
       <c r="A1069" s="2" t="inlineStr">
@@ -45280,10 +48760,20 @@
       <c r="G1071" s="2" t="n">
         <v>3.8</v>
       </c>
-      <c r="H1071" s="6" t="inlineStr"/>
-      <c r="I1071" s="6" t="inlineStr"/>
-      <c r="J1071" s="6" t="inlineStr"/>
-      <c r="K1071" s="6" t="inlineStr"/>
+      <c r="H1071" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1071" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1071" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K1071" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="1072">
       <c r="A1072" s="2" t="inlineStr">
@@ -45319,10 +48809,20 @@
       <c r="G1072" s="2" t="n">
         <v>1.81</v>
       </c>
-      <c r="H1072" s="6" t="inlineStr"/>
-      <c r="I1072" s="6" t="inlineStr"/>
-      <c r="J1072" s="6" t="inlineStr"/>
-      <c r="K1072" s="6" t="inlineStr"/>
+      <c r="H1072" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1072" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1072" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K1072" s="4" t="n">
+        <v>81</v>
+      </c>
     </row>
     <row r="1073">
       <c r="A1073" s="2" t="inlineStr">
@@ -45358,10 +48858,20 @@
       <c r="G1073" s="2" t="n">
         <v>4.5</v>
       </c>
-      <c r="H1073" s="6" t="inlineStr"/>
-      <c r="I1073" s="6" t="inlineStr"/>
-      <c r="J1073" s="6" t="inlineStr"/>
-      <c r="K1073" s="6" t="inlineStr"/>
+      <c r="H1073" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I1073" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1073" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K1073" s="5" t="n">
+        <v>-350</v>
+      </c>
     </row>
     <row r="1074">
       <c r="A1074" s="2" t="inlineStr">
@@ -45397,10 +48907,20 @@
       <c r="G1074" s="2" t="n">
         <v>4.5</v>
       </c>
-      <c r="H1074" s="6" t="inlineStr"/>
-      <c r="I1074" s="6" t="inlineStr"/>
-      <c r="J1074" s="6" t="inlineStr"/>
-      <c r="K1074" s="6" t="inlineStr"/>
+      <c r="H1074" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1074" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J1074" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K1074" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="1075">
       <c r="A1075" s="2" t="inlineStr">
@@ -45436,10 +48956,20 @@
       <c r="G1075" s="2" t="n">
         <v>3.8</v>
       </c>
-      <c r="H1075" s="6" t="inlineStr"/>
-      <c r="I1075" s="6" t="inlineStr"/>
-      <c r="J1075" s="6" t="inlineStr"/>
-      <c r="K1075" s="6" t="inlineStr"/>
+      <c r="H1075" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1075" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1075" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K1075" s="5" t="n">
+        <v>-280</v>
+      </c>
     </row>
     <row r="1076">
       <c r="A1076" s="2" t="inlineStr">
@@ -45475,10 +49005,20 @@
       <c r="G1076" s="2" t="n">
         <v>1.92</v>
       </c>
-      <c r="H1076" s="6" t="inlineStr"/>
-      <c r="I1076" s="6" t="inlineStr"/>
-      <c r="J1076" s="6" t="inlineStr"/>
-      <c r="K1076" s="6" t="inlineStr"/>
+      <c r="H1076" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1076" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1076" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K1076" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="1077">
       <c r="A1077" s="2" t="inlineStr">
@@ -45670,10 +49210,20 @@
       <c r="G1081" s="2" t="n">
         <v>1.91</v>
       </c>
-      <c r="H1081" s="6" t="inlineStr"/>
-      <c r="I1081" s="6" t="inlineStr"/>
-      <c r="J1081" s="6" t="inlineStr"/>
-      <c r="K1081" s="6" t="inlineStr"/>
+      <c r="H1081" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1081" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1081" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K1081" s="4" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="1082">
       <c r="A1082" s="2" t="inlineStr">
@@ -45709,10 +49259,20 @@
       <c r="G1082" s="2" t="n">
         <v>2.3</v>
       </c>
-      <c r="H1082" s="6" t="inlineStr"/>
-      <c r="I1082" s="6" t="inlineStr"/>
-      <c r="J1082" s="6" t="inlineStr"/>
-      <c r="K1082" s="6" t="inlineStr"/>
+      <c r="H1082" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1082" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1082" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K1082" s="5" t="n">
+        <v>-130</v>
+      </c>
     </row>
     <row r="1083">
       <c r="A1083" s="2" t="inlineStr">
@@ -45748,10 +49308,20 @@
       <c r="G1083" s="2" t="n">
         <v>9.4</v>
       </c>
-      <c r="H1083" s="6" t="inlineStr"/>
-      <c r="I1083" s="6" t="inlineStr"/>
-      <c r="J1083" s="6" t="inlineStr"/>
-      <c r="K1083" s="6" t="inlineStr"/>
+      <c r="H1083" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1083" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1083" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K1083" s="5" t="n">
+        <v>-840</v>
+      </c>
     </row>
     <row r="1084">
       <c r="A1084" s="2" t="inlineStr">
@@ -45787,10 +49357,20 @@
       <c r="G1084" s="2" t="n">
         <v>3.65</v>
       </c>
-      <c r="H1084" s="6" t="inlineStr"/>
-      <c r="I1084" s="6" t="inlineStr"/>
-      <c r="J1084" s="6" t="inlineStr"/>
-      <c r="K1084" s="6" t="inlineStr"/>
+      <c r="H1084" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1084" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1084" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K1084" s="5" t="n">
+        <v>-265</v>
+      </c>
     </row>
     <row r="1085">
       <c r="A1085" s="2" t="inlineStr">
@@ -45826,10 +49406,20 @@
       <c r="G1085" s="2" t="n">
         <v>2.58</v>
       </c>
-      <c r="H1085" s="6" t="inlineStr"/>
-      <c r="I1085" s="6" t="inlineStr"/>
-      <c r="J1085" s="6" t="inlineStr"/>
-      <c r="K1085" s="6" t="inlineStr"/>
+      <c r="H1085" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1085" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1085" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K1085" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="1086">
       <c r="A1086" s="2" t="inlineStr">
@@ -45865,10 +49455,20 @@
       <c r="G1086" s="2" t="n">
         <v>2.4</v>
       </c>
-      <c r="H1086" s="6" t="inlineStr"/>
-      <c r="I1086" s="6" t="inlineStr"/>
-      <c r="J1086" s="6" t="inlineStr"/>
-      <c r="K1086" s="6" t="inlineStr"/>
+      <c r="H1086" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1086" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1086" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K1086" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="1087">
       <c r="A1087" s="2" t="inlineStr">
@@ -46060,10 +49660,20 @@
       <c r="G1091" s="2" t="n">
         <v>2.8</v>
       </c>
-      <c r="H1091" s="6" t="inlineStr"/>
-      <c r="I1091" s="6" t="inlineStr"/>
-      <c r="J1091" s="6" t="inlineStr"/>
-      <c r="K1091" s="6" t="inlineStr"/>
+      <c r="H1091" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1091" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1091" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K1091" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="1092">
       <c r="A1092" s="2" t="inlineStr">
@@ -46099,10 +49709,20 @@
       <c r="G1092" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="H1092" s="6" t="inlineStr"/>
-      <c r="I1092" s="6" t="inlineStr"/>
-      <c r="J1092" s="6" t="inlineStr"/>
-      <c r="K1092" s="6" t="inlineStr"/>
+      <c r="H1092" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I1092" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1092" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K1092" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="1093">
       <c r="A1093" s="2" t="inlineStr">
@@ -46138,10 +49758,20 @@
       <c r="G1093" s="2" t="n">
         <v>2.04</v>
       </c>
-      <c r="H1093" s="6" t="inlineStr"/>
-      <c r="I1093" s="6" t="inlineStr"/>
-      <c r="J1093" s="6" t="inlineStr"/>
-      <c r="K1093" s="6" t="inlineStr"/>
+      <c r="H1093" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I1093" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1093" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K1093" s="4" t="n">
+        <v>104</v>
+      </c>
     </row>
     <row r="1094">
       <c r="A1094" s="2" t="inlineStr">
